--- a/artfynd/A 15392-2025 artfynd.xlsx
+++ b/artfynd/A 15392-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017034</v>
+        <v>125017014</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>74901</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514346</v>
+        <v>514311</v>
       </c>
       <c r="R2" t="n">
-        <v>6741714</v>
+        <v>6741920</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017081</v>
+        <v>125017085</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514370</v>
+        <v>514342</v>
       </c>
       <c r="R3" t="n">
-        <v>6742029</v>
+        <v>6742146</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017075</v>
+        <v>125017069</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514356</v>
+        <v>514232</v>
       </c>
       <c r="R4" t="n">
-        <v>6742004</v>
+        <v>6741754</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017078</v>
+        <v>125017083</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514359</v>
+        <v>514373</v>
       </c>
       <c r="R5" t="n">
-        <v>6742012</v>
+        <v>6741951</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017030</v>
+        <v>125017088</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
+        <v>5176</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,39 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514354</v>
+        <v>514339</v>
       </c>
       <c r="R7" t="n">
-        <v>6741952</v>
+        <v>6741763</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017016</v>
+        <v>125017027</v>
       </c>
       <c r="B8" t="n">
-        <v>90977</v>
+        <v>96979</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514278</v>
+        <v>514325</v>
       </c>
       <c r="R8" t="n">
-        <v>6741831</v>
+        <v>6742071</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017055</v>
+        <v>125017016</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1411,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514243</v>
+        <v>514278</v>
       </c>
       <c r="R9" t="n">
-        <v>6741837</v>
+        <v>6741831</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017053</v>
+        <v>125017043</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1541,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514273</v>
+        <v>514354</v>
       </c>
       <c r="R10" t="n">
-        <v>6741841</v>
+        <v>6742044</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017086</v>
+        <v>125017074</v>
       </c>
       <c r="B11" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1615,25 +1605,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514306</v>
+        <v>514374</v>
       </c>
       <c r="R11" t="n">
-        <v>6741916</v>
+        <v>6741981</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017074</v>
+        <v>125017049</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1745,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514374</v>
+        <v>514311</v>
       </c>
       <c r="R12" t="n">
-        <v>6741981</v>
+        <v>6741920</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017050</v>
+        <v>125017041</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1847,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514318</v>
+        <v>514235</v>
       </c>
       <c r="R13" t="n">
-        <v>6741915</v>
+        <v>6742182</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017046</v>
+        <v>125017021</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514337</v>
+        <v>514291</v>
       </c>
       <c r="R14" t="n">
-        <v>6741991</v>
+        <v>6741927</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017015</v>
+        <v>125017022</v>
       </c>
       <c r="B15" t="n">
-        <v>96354</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514225</v>
+        <v>514283</v>
       </c>
       <c r="R15" t="n">
-        <v>6741799</v>
+        <v>6741836</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2087,11 +2077,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2118,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017032</v>
+        <v>125017076</v>
       </c>
       <c r="B16" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2130,43 +2115,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514330</v>
+        <v>514359</v>
       </c>
       <c r="R16" t="n">
-        <v>6741874</v>
+        <v>6742010</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017036</v>
+        <v>125017048</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2237,47 +2217,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514293</v>
+        <v>514295</v>
       </c>
       <c r="R17" t="n">
-        <v>6742097</v>
+        <v>6741934</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,10 +2307,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017029</v>
+        <v>125017078</v>
       </c>
       <c r="B18" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,43 +2319,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514393</v>
+        <v>514359</v>
       </c>
       <c r="R18" t="n">
-        <v>6741939</v>
+        <v>6742012</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125017083</v>
+        <v>125017044</v>
       </c>
       <c r="B19" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2455,25 +2421,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2483,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514373</v>
+        <v>514351</v>
       </c>
       <c r="R19" t="n">
-        <v>6741951</v>
+        <v>6742013</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125017013</v>
+        <v>125017052</v>
       </c>
       <c r="B20" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2561,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2585,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514345</v>
+        <v>514274</v>
       </c>
       <c r="R20" t="n">
-        <v>6741942</v>
+        <v>6741848</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2647,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125017084</v>
+        <v>125017073</v>
       </c>
       <c r="B21" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2659,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2687,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514370</v>
+        <v>514387</v>
       </c>
       <c r="R21" t="n">
-        <v>6742063</v>
+        <v>6741982</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2749,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125017071</v>
+        <v>125017070</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2789,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514339</v>
+        <v>514333</v>
       </c>
       <c r="R22" t="n">
-        <v>6741763</v>
+        <v>6741764</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2851,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125017085</v>
+        <v>125017045</v>
       </c>
       <c r="B23" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2863,25 +2829,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2891,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514342</v>
+        <v>514340</v>
       </c>
       <c r="R23" t="n">
-        <v>6742146</v>
+        <v>6741996</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2953,10 +2919,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125017033</v>
+        <v>125017082</v>
       </c>
       <c r="B24" t="n">
-        <v>8447</v>
+        <v>92293</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2969,27 +2935,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2998,10 +2968,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514336</v>
+        <v>514343</v>
       </c>
       <c r="R24" t="n">
-        <v>6741710</v>
+        <v>6741717</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3060,10 +3030,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125017076</v>
+        <v>125017087</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3072,25 +3042,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3100,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514359</v>
+        <v>514358</v>
       </c>
       <c r="R25" t="n">
-        <v>6742010</v>
+        <v>6742011</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3162,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125017027</v>
+        <v>125017084</v>
       </c>
       <c r="B26" t="n">
-        <v>96979</v>
+        <v>96227</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3178,21 +3148,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>2869</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3202,10 +3172,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514325</v>
+        <v>514370</v>
       </c>
       <c r="R26" t="n">
-        <v>6742071</v>
+        <v>6742063</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3264,7 +3234,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125017043</v>
+        <v>125017054</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3304,10 +3274,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514354</v>
+        <v>514257</v>
       </c>
       <c r="R27" t="n">
-        <v>6742044</v>
+        <v>6741839</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3366,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125017022</v>
+        <v>125017037</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3382,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3406,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514283</v>
+        <v>514291</v>
       </c>
       <c r="R28" t="n">
-        <v>6741836</v>
+        <v>6741924</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3468,7 +3438,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125017048</v>
+        <v>125017040</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3508,10 +3478,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514295</v>
+        <v>514327</v>
       </c>
       <c r="R29" t="n">
-        <v>6741934</v>
+        <v>6741885</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3544,6 +3514,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3570,10 +3545,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125017025</v>
+        <v>125017051</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3586,21 +3561,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3610,10 +3585,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514390</v>
+        <v>514337</v>
       </c>
       <c r="R30" t="n">
-        <v>6741952</v>
+        <v>6741897</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3672,7 +3647,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125017044</v>
+        <v>125017042</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3712,10 +3687,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514351</v>
+        <v>514331</v>
       </c>
       <c r="R31" t="n">
-        <v>6742013</v>
+        <v>6742061</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3774,7 +3749,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125017051</v>
+        <v>125017055</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3814,10 +3789,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514337</v>
+        <v>514243</v>
       </c>
       <c r="R32" t="n">
-        <v>6741897</v>
+        <v>6741837</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3876,10 +3851,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125017087</v>
+        <v>125017025</v>
       </c>
       <c r="B33" t="n">
-        <v>5176</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3888,25 +3863,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3916,10 +3891,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514358</v>
+        <v>514390</v>
       </c>
       <c r="R33" t="n">
-        <v>6742011</v>
+        <v>6741952</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3978,10 +3953,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125017082</v>
+        <v>125017047</v>
       </c>
       <c r="B34" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3990,47 +3965,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514343</v>
+        <v>514334</v>
       </c>
       <c r="R34" t="n">
-        <v>6741717</v>
+        <v>6741981</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4196,10 +4162,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125017014</v>
+        <v>125017030</v>
       </c>
       <c r="B36" t="n">
-        <v>74901</v>
+        <v>8447</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4208,38 +4174,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514311</v>
+        <v>514354</v>
       </c>
       <c r="R36" t="n">
-        <v>6741920</v>
+        <v>6741952</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4298,10 +4269,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125017021</v>
+        <v>125017034</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>8447</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4310,38 +4281,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514291</v>
+        <v>514346</v>
       </c>
       <c r="R37" t="n">
-        <v>6741927</v>
+        <v>6741714</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4400,7 +4376,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125017069</v>
+        <v>125017046</v>
       </c>
       <c r="B38" t="n">
         <v>78810</v>
@@ -4440,10 +4416,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514232</v>
+        <v>514337</v>
       </c>
       <c r="R38" t="n">
-        <v>6741754</v>
+        <v>6741991</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4502,10 +4478,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125017047</v>
+        <v>125017015</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4518,21 +4494,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4542,10 +4518,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514334</v>
+        <v>514225</v>
       </c>
       <c r="R39" t="n">
-        <v>6741981</v>
+        <v>6741799</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4578,6 +4554,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4604,10 +4585,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125017041</v>
+        <v>125017032</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4616,38 +4597,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514235</v>
+        <v>514330</v>
       </c>
       <c r="R40" t="n">
-        <v>6742182</v>
+        <v>6741874</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4706,10 +4692,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125017049</v>
+        <v>125017013</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4722,21 +4708,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4746,10 +4732,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514311</v>
+        <v>514345</v>
       </c>
       <c r="R41" t="n">
-        <v>6741920</v>
+        <v>6741942</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4808,7 +4794,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125017042</v>
+        <v>125017050</v>
       </c>
       <c r="B42" t="n">
         <v>78810</v>
@@ -4848,10 +4834,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514331</v>
+        <v>514318</v>
       </c>
       <c r="R42" t="n">
-        <v>6742061</v>
+        <v>6741915</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4910,10 +4896,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125017037</v>
+        <v>125017081</v>
       </c>
       <c r="B43" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4926,21 +4912,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4950,10 +4936,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514291</v>
+        <v>514370</v>
       </c>
       <c r="R43" t="n">
-        <v>6741924</v>
+        <v>6742029</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5119,10 +5105,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125017070</v>
+        <v>125017036</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5131,38 +5117,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514333</v>
+        <v>514293</v>
       </c>
       <c r="R45" t="n">
-        <v>6741764</v>
+        <v>6742097</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5221,7 +5216,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125017073</v>
+        <v>125017072</v>
       </c>
       <c r="B46" t="n">
         <v>78810</v>
@@ -5261,10 +5256,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514387</v>
+        <v>514411</v>
       </c>
       <c r="R46" t="n">
-        <v>6741982</v>
+        <v>6741898</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5323,7 +5318,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125017052</v>
+        <v>125017071</v>
       </c>
       <c r="B47" t="n">
         <v>78810</v>
@@ -5363,10 +5358,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514274</v>
+        <v>514339</v>
       </c>
       <c r="R47" t="n">
-        <v>6741848</v>
+        <v>6741763</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5425,10 +5420,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125017088</v>
+        <v>125017033</v>
       </c>
       <c r="B48" t="n">
-        <v>5176</v>
+        <v>8447</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5441,34 +5436,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514339</v>
+        <v>514336</v>
       </c>
       <c r="R48" t="n">
-        <v>6741763</v>
+        <v>6741710</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5527,7 +5527,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125017045</v>
+        <v>125017075</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514340</v>
+        <v>514356</v>
       </c>
       <c r="R49" t="n">
-        <v>6741996</v>
+        <v>6742004</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5629,7 +5629,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125017054</v>
+        <v>125017053</v>
       </c>
       <c r="B50" t="n">
         <v>78810</v>
@@ -5669,10 +5669,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514257</v>
+        <v>514273</v>
       </c>
       <c r="R50" t="n">
-        <v>6741839</v>
+        <v>6741841</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5731,10 +5731,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125017072</v>
+        <v>125017086</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5743,25 +5743,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514411</v>
+        <v>514306</v>
       </c>
       <c r="R51" t="n">
-        <v>6741898</v>
+        <v>6741916</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5833,10 +5833,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125017040</v>
+        <v>125017029</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5845,38 +5845,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514327</v>
+        <v>514393</v>
       </c>
       <c r="R52" t="n">
-        <v>6741885</v>
+        <v>6741939</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5909,11 +5914,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 15392-2025 artfynd.xlsx
+++ b/artfynd/A 15392-2025 artfynd.xlsx
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017022</v>
+        <v>125017076</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514283</v>
+        <v>514359</v>
       </c>
       <c r="R15" t="n">
-        <v>6741836</v>
+        <v>6742010</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017076</v>
+        <v>125017022</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514359</v>
+        <v>514283</v>
       </c>
       <c r="R16" t="n">
-        <v>6742010</v>
+        <v>6741836</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125017037</v>
+        <v>125017051</v>
       </c>
       <c r="B28" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3352,21 +3352,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514291</v>
+        <v>514337</v>
       </c>
       <c r="R28" t="n">
-        <v>6741924</v>
+        <v>6741897</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,7 +3438,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125017040</v>
+        <v>125017042</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514327</v>
+        <v>514331</v>
       </c>
       <c r="R29" t="n">
-        <v>6741885</v>
+        <v>6742061</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3514,11 +3514,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3545,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125017051</v>
+        <v>125017037</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3561,21 +3556,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3585,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514337</v>
+        <v>514291</v>
       </c>
       <c r="R30" t="n">
-        <v>6741897</v>
+        <v>6741924</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3647,7 +3642,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125017042</v>
+        <v>125017055</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3687,10 +3682,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514331</v>
+        <v>514243</v>
       </c>
       <c r="R31" t="n">
-        <v>6742061</v>
+        <v>6741837</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3749,7 +3744,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125017055</v>
+        <v>125017040</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3789,10 +3784,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514243</v>
+        <v>514327</v>
       </c>
       <c r="R32" t="n">
-        <v>6741837</v>
+        <v>6741885</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3825,6 +3820,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 15392-2025 artfynd.xlsx
+++ b/artfynd/A 15392-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017014</v>
+        <v>125017036</v>
       </c>
       <c r="B2" t="n">
-        <v>74901</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514311</v>
+        <v>514293</v>
       </c>
       <c r="R2" t="n">
-        <v>6741920</v>
+        <v>6742097</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017085</v>
+        <v>125017031</v>
       </c>
       <c r="B3" t="n">
-        <v>96227</v>
+        <v>8447</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +802,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2869</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514342</v>
+        <v>514358</v>
       </c>
       <c r="R3" t="n">
-        <v>6742146</v>
+        <v>6741952</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017069</v>
+        <v>125017032</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +905,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514232</v>
+        <v>514330</v>
       </c>
       <c r="R4" t="n">
-        <v>6741754</v>
+        <v>6741874</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017083</v>
+        <v>125017053</v>
       </c>
       <c r="B5" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +1012,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514373</v>
+        <v>514273</v>
       </c>
       <c r="R5" t="n">
-        <v>6741951</v>
+        <v>6741841</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1102,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017080</v>
+        <v>125017051</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1123,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514363</v>
+        <v>514337</v>
       </c>
       <c r="R6" t="n">
-        <v>6742014</v>
+        <v>6741897</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017088</v>
+        <v>125017085</v>
       </c>
       <c r="B7" t="n">
-        <v>5176</v>
+        <v>96227</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1220,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514339</v>
+        <v>514342</v>
       </c>
       <c r="R7" t="n">
-        <v>6741763</v>
+        <v>6742146</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017027</v>
+        <v>125017047</v>
       </c>
       <c r="B8" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1318,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514325</v>
+        <v>514334</v>
       </c>
       <c r="R8" t="n">
-        <v>6742071</v>
+        <v>6741981</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017016</v>
+        <v>125017078</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1420,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1448,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514278</v>
+        <v>514359</v>
       </c>
       <c r="R9" t="n">
-        <v>6741831</v>
+        <v>6742012</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017043</v>
+        <v>125017086</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1522,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514354</v>
+        <v>514306</v>
       </c>
       <c r="R10" t="n">
-        <v>6742044</v>
+        <v>6741916</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017074</v>
+        <v>125017029</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,38 +1624,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514374</v>
+        <v>514393</v>
       </c>
       <c r="R11" t="n">
-        <v>6741981</v>
+        <v>6741939</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1719,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017049</v>
+        <v>125017050</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1735,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514311</v>
+        <v>514318</v>
       </c>
       <c r="R12" t="n">
-        <v>6741920</v>
+        <v>6741915</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1821,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017041</v>
+        <v>125017088</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1833,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514235</v>
+        <v>514339</v>
       </c>
       <c r="R13" t="n">
-        <v>6742182</v>
+        <v>6741763</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017021</v>
+        <v>125017069</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1939,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514291</v>
+        <v>514232</v>
       </c>
       <c r="R14" t="n">
-        <v>6741927</v>
+        <v>6741754</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2025,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017076</v>
+        <v>125017072</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2041,10 +2065,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514359</v>
+        <v>514411</v>
       </c>
       <c r="R15" t="n">
-        <v>6742010</v>
+        <v>6741898</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017022</v>
+        <v>125017087</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>5176</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2139,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2167,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514283</v>
+        <v>514358</v>
       </c>
       <c r="R16" t="n">
-        <v>6741836</v>
+        <v>6742011</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2229,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017048</v>
+        <v>125017033</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,38 +2241,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514295</v>
+        <v>514336</v>
       </c>
       <c r="R17" t="n">
-        <v>6741934</v>
+        <v>6741710</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2336,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017078</v>
+        <v>125017071</v>
       </c>
       <c r="B18" t="n">
         <v>78810</v>
@@ -2347,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514359</v>
+        <v>514339</v>
       </c>
       <c r="R18" t="n">
-        <v>6742012</v>
+        <v>6741763</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,7 +2438,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125017044</v>
+        <v>125017042</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2449,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514351</v>
+        <v>514331</v>
       </c>
       <c r="R19" t="n">
-        <v>6742013</v>
+        <v>6742061</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,7 +2540,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125017052</v>
+        <v>125017040</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2551,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514274</v>
+        <v>514327</v>
       </c>
       <c r="R20" t="n">
-        <v>6741848</v>
+        <v>6741885</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2587,6 +2616,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2613,10 +2647,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125017073</v>
+        <v>125017082</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,38 +2659,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514387</v>
+        <v>514343</v>
       </c>
       <c r="R21" t="n">
-        <v>6741982</v>
+        <v>6741717</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,10 +2758,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125017070</v>
+        <v>125017015</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2774,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2798,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514333</v>
+        <v>514225</v>
       </c>
       <c r="R22" t="n">
-        <v>6741764</v>
+        <v>6741799</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2791,6 +2834,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2817,10 +2865,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125017045</v>
+        <v>125017034</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2829,38 +2877,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514340</v>
+        <v>514346</v>
       </c>
       <c r="R23" t="n">
-        <v>6741996</v>
+        <v>6741714</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,10 +2972,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125017082</v>
+        <v>125017035</v>
       </c>
       <c r="B24" t="n">
-        <v>92293</v>
+        <v>8447</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2935,31 +2988,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2968,10 +3017,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514343</v>
+        <v>514366</v>
       </c>
       <c r="R24" t="n">
-        <v>6741717</v>
+        <v>6741941</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,10 +3079,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125017087</v>
+        <v>125017052</v>
       </c>
       <c r="B25" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3042,25 +3091,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3070,10 +3119,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514358</v>
+        <v>514274</v>
       </c>
       <c r="R25" t="n">
-        <v>6742011</v>
+        <v>6741848</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,10 +3181,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125017084</v>
+        <v>125017043</v>
       </c>
       <c r="B26" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3144,25 +3193,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3172,10 +3221,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514370</v>
+        <v>514354</v>
       </c>
       <c r="R26" t="n">
-        <v>6742063</v>
+        <v>6742044</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3234,10 +3283,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125017054</v>
+        <v>125017016</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3246,25 +3295,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3274,10 +3323,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514257</v>
+        <v>514278</v>
       </c>
       <c r="R27" t="n">
-        <v>6741839</v>
+        <v>6741831</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3336,7 +3385,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125017051</v>
+        <v>125017081</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3376,10 +3425,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514337</v>
+        <v>514370</v>
       </c>
       <c r="R28" t="n">
-        <v>6741897</v>
+        <v>6742029</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3438,7 +3487,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125017042</v>
+        <v>125017080</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3478,10 +3527,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514331</v>
+        <v>514363</v>
       </c>
       <c r="R29" t="n">
-        <v>6742061</v>
+        <v>6742014</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3540,10 +3589,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125017037</v>
+        <v>125017013</v>
       </c>
       <c r="B30" t="n">
-        <v>91030</v>
+        <v>79428</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3556,21 +3605,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3580,10 +3629,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514291</v>
+        <v>514345</v>
       </c>
       <c r="R30" t="n">
-        <v>6741924</v>
+        <v>6741942</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3642,7 +3691,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125017055</v>
+        <v>125017054</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3682,10 +3731,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514243</v>
+        <v>514257</v>
       </c>
       <c r="R31" t="n">
-        <v>6741837</v>
+        <v>6741839</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3744,7 +3793,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125017040</v>
+        <v>125017074</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3784,10 +3833,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514327</v>
+        <v>514374</v>
       </c>
       <c r="R32" t="n">
-        <v>6741885</v>
+        <v>6741981</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3820,11 +3869,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3851,10 +3895,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125017025</v>
+        <v>125017037</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3867,21 +3911,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3891,10 +3935,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514390</v>
+        <v>514291</v>
       </c>
       <c r="R33" t="n">
-        <v>6741952</v>
+        <v>6741924</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3953,7 +3997,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125017047</v>
+        <v>125017075</v>
       </c>
       <c r="B34" t="n">
         <v>78810</v>
@@ -3993,10 +4037,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514334</v>
+        <v>514356</v>
       </c>
       <c r="R34" t="n">
-        <v>6741981</v>
+        <v>6742004</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4055,10 +4099,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125017031</v>
+        <v>125017044</v>
       </c>
       <c r="B35" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4067,43 +4111,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514358</v>
+        <v>514351</v>
       </c>
       <c r="R35" t="n">
-        <v>6741952</v>
+        <v>6742013</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4162,10 +4201,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125017030</v>
+        <v>125017049</v>
       </c>
       <c r="B36" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4174,43 +4213,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514354</v>
+        <v>514311</v>
       </c>
       <c r="R36" t="n">
-        <v>6741952</v>
+        <v>6741920</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4269,10 +4303,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125017034</v>
+        <v>125017084</v>
       </c>
       <c r="B37" t="n">
-        <v>8447</v>
+        <v>96227</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4285,39 +4319,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>2869</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514346</v>
+        <v>514370</v>
       </c>
       <c r="R37" t="n">
-        <v>6741714</v>
+        <v>6742063</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4376,10 +4405,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125017046</v>
+        <v>125017025</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4392,21 +4421,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4416,10 +4445,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514337</v>
+        <v>514390</v>
       </c>
       <c r="R38" t="n">
-        <v>6741991</v>
+        <v>6741952</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4478,10 +4507,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125017015</v>
+        <v>125017073</v>
       </c>
       <c r="B39" t="n">
-        <v>96354</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4494,21 +4523,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4518,10 +4547,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514225</v>
+        <v>514387</v>
       </c>
       <c r="R39" t="n">
-        <v>6741799</v>
+        <v>6741982</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4554,11 +4583,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4585,10 +4609,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125017032</v>
+        <v>125017076</v>
       </c>
       <c r="B40" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4597,43 +4621,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514330</v>
+        <v>514359</v>
       </c>
       <c r="R40" t="n">
-        <v>6741874</v>
+        <v>6742010</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4692,10 +4711,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125017013</v>
+        <v>125017083</v>
       </c>
       <c r="B41" t="n">
-        <v>79428</v>
+        <v>96227</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4704,25 +4723,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>2869</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4732,10 +4751,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514345</v>
+        <v>514373</v>
       </c>
       <c r="R41" t="n">
-        <v>6741942</v>
+        <v>6741951</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4794,10 +4813,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125017050</v>
+        <v>125017014</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4810,21 +4829,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4834,10 +4853,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514318</v>
+        <v>514311</v>
       </c>
       <c r="R42" t="n">
-        <v>6741915</v>
+        <v>6741920</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4896,10 +4915,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125017081</v>
+        <v>125017021</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4912,21 +4931,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4936,10 +4955,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514370</v>
+        <v>514291</v>
       </c>
       <c r="R43" t="n">
-        <v>6742029</v>
+        <v>6741927</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4998,10 +5017,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125017035</v>
+        <v>125017046</v>
       </c>
       <c r="B44" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5010,43 +5029,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514366</v>
+        <v>514337</v>
       </c>
       <c r="R44" t="n">
-        <v>6741941</v>
+        <v>6741991</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5105,10 +5119,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125017036</v>
+        <v>125017070</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5117,47 +5131,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514293</v>
+        <v>514333</v>
       </c>
       <c r="R45" t="n">
-        <v>6742097</v>
+        <v>6741764</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5216,7 +5221,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125017072</v>
+        <v>125017045</v>
       </c>
       <c r="B46" t="n">
         <v>78810</v>
@@ -5256,10 +5261,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514411</v>
+        <v>514340</v>
       </c>
       <c r="R46" t="n">
-        <v>6741898</v>
+        <v>6741996</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5318,7 +5323,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125017071</v>
+        <v>125017041</v>
       </c>
       <c r="B47" t="n">
         <v>78810</v>
@@ -5358,10 +5363,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514339</v>
+        <v>514235</v>
       </c>
       <c r="R47" t="n">
-        <v>6741763</v>
+        <v>6742182</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5420,10 +5425,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125017033</v>
+        <v>125017027</v>
       </c>
       <c r="B48" t="n">
-        <v>8447</v>
+        <v>96979</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5436,39 +5441,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514336</v>
+        <v>514325</v>
       </c>
       <c r="R48" t="n">
-        <v>6741710</v>
+        <v>6742071</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5527,7 +5527,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125017075</v>
+        <v>125017055</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -5567,10 +5567,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514356</v>
+        <v>514243</v>
       </c>
       <c r="R49" t="n">
-        <v>6742004</v>
+        <v>6741837</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5629,7 +5629,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125017053</v>
+        <v>125017048</v>
       </c>
       <c r="B50" t="n">
         <v>78810</v>
@@ -5669,10 +5669,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514273</v>
+        <v>514295</v>
       </c>
       <c r="R50" t="n">
-        <v>6741841</v>
+        <v>6741934</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5731,10 +5731,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125017086</v>
+        <v>125017022</v>
       </c>
       <c r="B51" t="n">
-        <v>5176</v>
+        <v>91012</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5743,25 +5743,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5771,10 +5771,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514306</v>
+        <v>514283</v>
       </c>
       <c r="R51" t="n">
-        <v>6741916</v>
+        <v>6741836</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5833,7 +5833,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125017029</v>
+        <v>125017030</v>
       </c>
       <c r="B52" t="n">
         <v>8447</v>
@@ -5878,10 +5878,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514393</v>
+        <v>514354</v>
       </c>
       <c r="R52" t="n">
-        <v>6741939</v>
+        <v>6741952</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 15392-2025 artfynd.xlsx
+++ b/artfynd/A 15392-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017036</v>
+        <v>125017051</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514293</v>
+        <v>514337</v>
       </c>
       <c r="R2" t="n">
-        <v>6742097</v>
+        <v>6741897</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017031</v>
+        <v>125017036</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,31 +789,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514358</v>
+        <v>514293</v>
       </c>
       <c r="R3" t="n">
-        <v>6741952</v>
+        <v>6742097</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -893,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017032</v>
+        <v>125017031</v>
       </c>
       <c r="B4" t="n">
         <v>8447</v>
@@ -929,7 +924,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -938,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514330</v>
+        <v>514358</v>
       </c>
       <c r="R4" t="n">
-        <v>6741874</v>
+        <v>6741952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017053</v>
+        <v>125017032</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,38 +1007,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514273</v>
+        <v>514330</v>
       </c>
       <c r="R5" t="n">
-        <v>6741841</v>
+        <v>6741874</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,7 +1102,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017051</v>
+        <v>125017053</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514337</v>
+        <v>514273</v>
       </c>
       <c r="R6" t="n">
-        <v>6741897</v>
+        <v>6741841</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1306,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017047</v>
+        <v>125017086</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,25 +1318,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514334</v>
+        <v>514306</v>
       </c>
       <c r="R8" t="n">
-        <v>6741981</v>
+        <v>6741916</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017078</v>
+        <v>125017029</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,38 +1420,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514359</v>
+        <v>514393</v>
       </c>
       <c r="R9" t="n">
-        <v>6742012</v>
+        <v>6741939</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017086</v>
+        <v>125017047</v>
       </c>
       <c r="B10" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,25 +1527,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1550,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514306</v>
+        <v>514334</v>
       </c>
       <c r="R10" t="n">
-        <v>6741916</v>
+        <v>6741981</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,10 +1617,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017029</v>
+        <v>125017078</v>
       </c>
       <c r="B11" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,43 +1629,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514393</v>
+        <v>514359</v>
       </c>
       <c r="R11" t="n">
-        <v>6741939</v>
+        <v>6742012</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2540,10 +2540,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125017040</v>
+        <v>125017082</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,38 +2552,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514327</v>
+        <v>514343</v>
       </c>
       <c r="R20" t="n">
-        <v>6741885</v>
+        <v>6741717</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2616,11 +2625,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2647,10 +2651,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125017082</v>
+        <v>125017015</v>
       </c>
       <c r="B21" t="n">
-        <v>92293</v>
+        <v>96354</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2659,47 +2663,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514343</v>
+        <v>514225</v>
       </c>
       <c r="R21" t="n">
-        <v>6741717</v>
+        <v>6741799</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2732,6 +2727,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2758,10 +2758,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125017015</v>
+        <v>125017040</v>
       </c>
       <c r="B22" t="n">
-        <v>96354</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2774,21 +2774,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514225</v>
+        <v>514327</v>
       </c>
       <c r="R22" t="n">
-        <v>6741799</v>
+        <v>6741885</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På låga i röjd sumpskog</t>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4507,7 +4507,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125017073</v>
+        <v>125017076</v>
       </c>
       <c r="B39" t="n">
         <v>78810</v>
@@ -4547,10 +4547,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514387</v>
+        <v>514359</v>
       </c>
       <c r="R39" t="n">
-        <v>6741982</v>
+        <v>6742010</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4609,7 +4609,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125017076</v>
+        <v>125017073</v>
       </c>
       <c r="B40" t="n">
         <v>78810</v>
@@ -4649,10 +4649,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514359</v>
+        <v>514387</v>
       </c>
       <c r="R40" t="n">
-        <v>6742010</v>
+        <v>6741982</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4915,10 +4915,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125017021</v>
+        <v>125017046</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4931,21 +4931,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514291</v>
+        <v>514337</v>
       </c>
       <c r="R43" t="n">
-        <v>6741927</v>
+        <v>6741991</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5017,10 +5017,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125017046</v>
+        <v>125017021</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5033,21 +5033,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5057,10 +5057,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514337</v>
+        <v>514291</v>
       </c>
       <c r="R44" t="n">
-        <v>6741991</v>
+        <v>6741927</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5119,7 +5119,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125017070</v>
+        <v>125017045</v>
       </c>
       <c r="B45" t="n">
         <v>78810</v>
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514333</v>
+        <v>514340</v>
       </c>
       <c r="R45" t="n">
-        <v>6741764</v>
+        <v>6741996</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5221,7 +5221,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125017045</v>
+        <v>125017070</v>
       </c>
       <c r="B46" t="n">
         <v>78810</v>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514340</v>
+        <v>514333</v>
       </c>
       <c r="R46" t="n">
-        <v>6741996</v>
+        <v>6741764</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>

--- a/artfynd/A 15392-2025 artfynd.xlsx
+++ b/artfynd/A 15392-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017051</v>
+        <v>125017034</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514337</v>
+        <v>514346</v>
       </c>
       <c r="R2" t="n">
-        <v>6741897</v>
+        <v>6741714</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017036</v>
+        <v>125017081</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,47 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514293</v>
+        <v>514370</v>
       </c>
       <c r="R3" t="n">
-        <v>6742097</v>
+        <v>6742029</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017031</v>
+        <v>125017021</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,43 +896,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514358</v>
+        <v>514291</v>
       </c>
       <c r="R4" t="n">
-        <v>6741952</v>
+        <v>6741927</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017032</v>
+        <v>125017014</v>
       </c>
       <c r="B5" t="n">
-        <v>8447</v>
+        <v>74901</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,43 +998,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514330</v>
+        <v>514311</v>
       </c>
       <c r="R5" t="n">
-        <v>6741874</v>
+        <v>6741920</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017053</v>
+        <v>125017035</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,38 +1100,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514273</v>
+        <v>514366</v>
       </c>
       <c r="R6" t="n">
-        <v>6741841</v>
+        <v>6741941</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017085</v>
+        <v>125017027</v>
       </c>
       <c r="B7" t="n">
-        <v>96227</v>
+        <v>96979</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1244,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514342</v>
+        <v>514325</v>
       </c>
       <c r="R7" t="n">
-        <v>6742146</v>
+        <v>6742071</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017086</v>
+        <v>125017036</v>
       </c>
       <c r="B8" t="n">
-        <v>5176</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,38 +1309,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514306</v>
+        <v>514293</v>
       </c>
       <c r="R8" t="n">
-        <v>6741916</v>
+        <v>6742097</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017029</v>
+        <v>125017052</v>
       </c>
       <c r="B9" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,43 +1420,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514393</v>
+        <v>514274</v>
       </c>
       <c r="R9" t="n">
-        <v>6741939</v>
+        <v>6741848</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,7 +1510,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017047</v>
+        <v>125017042</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1555,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514334</v>
+        <v>514331</v>
       </c>
       <c r="R10" t="n">
-        <v>6741981</v>
+        <v>6742061</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1617,7 +1612,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017078</v>
+        <v>125017050</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1657,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514359</v>
+        <v>514318</v>
       </c>
       <c r="R11" t="n">
-        <v>6742012</v>
+        <v>6741915</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,7 +1714,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017050</v>
+        <v>125017041</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1759,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514318</v>
+        <v>514235</v>
       </c>
       <c r="R12" t="n">
-        <v>6741915</v>
+        <v>6742182</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,10 +1816,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017088</v>
+        <v>125017048</v>
       </c>
       <c r="B13" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,25 +1828,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,10 +1856,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514339</v>
+        <v>514295</v>
       </c>
       <c r="R13" t="n">
-        <v>6741763</v>
+        <v>6741934</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,10 +1918,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017069</v>
+        <v>125017015</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,21 +1934,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1963,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514232</v>
+        <v>514225</v>
       </c>
       <c r="R14" t="n">
-        <v>6741754</v>
+        <v>6741799</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,6 +1994,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2025,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017072</v>
+        <v>125017037</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2041,21 +2041,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514411</v>
+        <v>514291</v>
       </c>
       <c r="R15" t="n">
-        <v>6741898</v>
+        <v>6741924</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017087</v>
+        <v>125017078</v>
       </c>
       <c r="B16" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2139,25 +2139,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514358</v>
+        <v>514359</v>
       </c>
       <c r="R16" t="n">
-        <v>6742011</v>
+        <v>6742012</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,10 +2229,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017033</v>
+        <v>125017049</v>
       </c>
       <c r="B17" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,43 +2241,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514336</v>
+        <v>514311</v>
       </c>
       <c r="R17" t="n">
-        <v>6741710</v>
+        <v>6741920</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,10 +2331,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017071</v>
+        <v>125017031</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,38 +2343,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514339</v>
+        <v>514358</v>
       </c>
       <c r="R18" t="n">
-        <v>6741763</v>
+        <v>6741952</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125017042</v>
+        <v>125017086</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,25 +2450,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514331</v>
+        <v>514306</v>
       </c>
       <c r="R19" t="n">
-        <v>6742061</v>
+        <v>6741916</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,10 +2540,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125017082</v>
+        <v>125017025</v>
       </c>
       <c r="B20" t="n">
-        <v>92293</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,47 +2552,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514343</v>
+        <v>514390</v>
       </c>
       <c r="R20" t="n">
-        <v>6741717</v>
+        <v>6741952</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,10 +2642,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125017015</v>
+        <v>125017071</v>
       </c>
       <c r="B21" t="n">
-        <v>96354</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2667,21 +2658,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2691,10 +2682,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514225</v>
+        <v>514339</v>
       </c>
       <c r="R21" t="n">
-        <v>6741799</v>
+        <v>6741763</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2727,11 +2718,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2758,7 +2744,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125017040</v>
+        <v>125017043</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2798,10 +2784,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514327</v>
+        <v>514354</v>
       </c>
       <c r="R22" t="n">
-        <v>6741885</v>
+        <v>6742044</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2834,11 +2820,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2865,10 +2846,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125017034</v>
+        <v>125017072</v>
       </c>
       <c r="B23" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2877,43 +2858,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514346</v>
+        <v>514411</v>
       </c>
       <c r="R23" t="n">
-        <v>6741714</v>
+        <v>6741898</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2972,10 +2948,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125017035</v>
+        <v>125017055</v>
       </c>
       <c r="B24" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2984,43 +2960,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514366</v>
+        <v>514243</v>
       </c>
       <c r="R24" t="n">
-        <v>6741941</v>
+        <v>6741837</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3079,10 +3050,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125017052</v>
+        <v>125017032</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3091,38 +3062,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514274</v>
+        <v>514330</v>
       </c>
       <c r="R25" t="n">
-        <v>6741848</v>
+        <v>6741874</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,7 +3157,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125017043</v>
+        <v>125017051</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3221,10 +3197,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514354</v>
+        <v>514337</v>
       </c>
       <c r="R26" t="n">
-        <v>6742044</v>
+        <v>6741897</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3283,10 +3259,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125017016</v>
+        <v>125017075</v>
       </c>
       <c r="B27" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3295,25 +3271,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3323,10 +3299,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514278</v>
+        <v>514356</v>
       </c>
       <c r="R27" t="n">
-        <v>6741831</v>
+        <v>6742004</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3385,7 +3361,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125017081</v>
+        <v>125017069</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3425,10 +3401,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514370</v>
+        <v>514232</v>
       </c>
       <c r="R28" t="n">
-        <v>6742029</v>
+        <v>6741754</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3487,7 +3463,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125017080</v>
+        <v>125017040</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3527,10 +3503,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514363</v>
+        <v>514327</v>
       </c>
       <c r="R29" t="n">
-        <v>6742014</v>
+        <v>6741885</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3563,6 +3539,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3589,10 +3570,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125017013</v>
+        <v>125017087</v>
       </c>
       <c r="B30" t="n">
-        <v>79428</v>
+        <v>5176</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3601,25 +3582,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3629,10 +3610,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514345</v>
+        <v>514358</v>
       </c>
       <c r="R30" t="n">
-        <v>6741942</v>
+        <v>6742011</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3691,10 +3672,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125017054</v>
+        <v>125017033</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3703,38 +3684,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514257</v>
+        <v>514336</v>
       </c>
       <c r="R31" t="n">
-        <v>6741839</v>
+        <v>6741710</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3793,7 +3779,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125017074</v>
+        <v>125017054</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3833,10 +3819,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514374</v>
+        <v>514257</v>
       </c>
       <c r="R32" t="n">
-        <v>6741981</v>
+        <v>6741839</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3895,10 +3881,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125017037</v>
+        <v>125017030</v>
       </c>
       <c r="B33" t="n">
-        <v>91030</v>
+        <v>8447</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3907,38 +3893,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514291</v>
+        <v>514354</v>
       </c>
       <c r="R33" t="n">
-        <v>6741924</v>
+        <v>6741952</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3997,10 +3988,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125017075</v>
+        <v>125017029</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4009,38 +4000,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514356</v>
+        <v>514393</v>
       </c>
       <c r="R34" t="n">
-        <v>6742004</v>
+        <v>6741939</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4099,7 +4095,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125017044</v>
+        <v>125017076</v>
       </c>
       <c r="B35" t="n">
         <v>78810</v>
@@ -4139,10 +4135,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514351</v>
+        <v>514359</v>
       </c>
       <c r="R35" t="n">
-        <v>6742013</v>
+        <v>6742010</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4201,10 +4197,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125017049</v>
+        <v>125017084</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4213,25 +4209,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4241,10 +4237,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514311</v>
+        <v>514370</v>
       </c>
       <c r="R36" t="n">
-        <v>6741920</v>
+        <v>6742063</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4303,10 +4299,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125017084</v>
+        <v>125017046</v>
       </c>
       <c r="B37" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4315,25 +4311,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4343,10 +4339,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514370</v>
+        <v>514337</v>
       </c>
       <c r="R37" t="n">
-        <v>6742063</v>
+        <v>6741991</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4405,10 +4401,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125017025</v>
+        <v>125017047</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4421,21 +4417,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4445,10 +4441,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514390</v>
+        <v>514334</v>
       </c>
       <c r="R38" t="n">
-        <v>6741952</v>
+        <v>6741981</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4507,7 +4503,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125017076</v>
+        <v>125017070</v>
       </c>
       <c r="B39" t="n">
         <v>78810</v>
@@ -4547,10 +4543,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514359</v>
+        <v>514333</v>
       </c>
       <c r="R39" t="n">
-        <v>6742010</v>
+        <v>6741764</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4609,10 +4605,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125017073</v>
+        <v>125017022</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4625,21 +4621,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4649,10 +4645,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514387</v>
+        <v>514283</v>
       </c>
       <c r="R40" t="n">
-        <v>6741982</v>
+        <v>6741836</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4711,10 +4707,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125017083</v>
+        <v>125017045</v>
       </c>
       <c r="B41" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4723,25 +4719,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4751,10 +4747,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514373</v>
+        <v>514340</v>
       </c>
       <c r="R41" t="n">
-        <v>6741951</v>
+        <v>6741996</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4813,10 +4809,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125017014</v>
+        <v>125017088</v>
       </c>
       <c r="B42" t="n">
-        <v>74901</v>
+        <v>5176</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4825,25 +4821,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4853,10 +4849,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514311</v>
+        <v>514339</v>
       </c>
       <c r="R42" t="n">
-        <v>6741920</v>
+        <v>6741763</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4915,10 +4911,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125017046</v>
+        <v>125017082</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4927,38 +4923,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514337</v>
+        <v>514343</v>
       </c>
       <c r="R43" t="n">
-        <v>6741991</v>
+        <v>6741717</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5017,10 +5022,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125017021</v>
+        <v>125017053</v>
       </c>
       <c r="B44" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5033,21 +5038,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5057,10 +5062,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514291</v>
+        <v>514273</v>
       </c>
       <c r="R44" t="n">
-        <v>6741927</v>
+        <v>6741841</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5119,7 +5124,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125017045</v>
+        <v>125017044</v>
       </c>
       <c r="B45" t="n">
         <v>78810</v>
@@ -5159,10 +5164,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514340</v>
+        <v>514351</v>
       </c>
       <c r="R45" t="n">
-        <v>6741996</v>
+        <v>6742013</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5221,10 +5226,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125017070</v>
+        <v>125017013</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5237,21 +5242,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5261,10 +5266,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514333</v>
+        <v>514345</v>
       </c>
       <c r="R46" t="n">
-        <v>6741764</v>
+        <v>6741942</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5323,7 +5328,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125017041</v>
+        <v>125017073</v>
       </c>
       <c r="B47" t="n">
         <v>78810</v>
@@ -5363,10 +5368,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514235</v>
+        <v>514387</v>
       </c>
       <c r="R47" t="n">
-        <v>6742182</v>
+        <v>6741982</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5425,10 +5430,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125017027</v>
+        <v>125017083</v>
       </c>
       <c r="B48" t="n">
-        <v>96979</v>
+        <v>96227</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5441,21 +5446,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>2869</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5465,10 +5470,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514325</v>
+        <v>514373</v>
       </c>
       <c r="R48" t="n">
-        <v>6742071</v>
+        <v>6741951</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5527,7 +5532,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125017055</v>
+        <v>125017074</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -5567,10 +5572,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514243</v>
+        <v>514374</v>
       </c>
       <c r="R49" t="n">
-        <v>6741837</v>
+        <v>6741981</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5629,10 +5634,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125017048</v>
+        <v>125017085</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5641,25 +5646,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5669,10 +5674,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514295</v>
+        <v>514342</v>
       </c>
       <c r="R50" t="n">
-        <v>6741934</v>
+        <v>6742146</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5731,10 +5736,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125017022</v>
+        <v>125017016</v>
       </c>
       <c r="B51" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5743,25 +5748,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5771,10 +5776,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514283</v>
+        <v>514278</v>
       </c>
       <c r="R51" t="n">
-        <v>6741836</v>
+        <v>6741831</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5833,10 +5838,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125017030</v>
+        <v>125017080</v>
       </c>
       <c r="B52" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5845,43 +5850,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514354</v>
+        <v>514363</v>
       </c>
       <c r="R52" t="n">
-        <v>6741952</v>
+        <v>6742014</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 15392-2025 artfynd.xlsx
+++ b/artfynd/A 15392-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017034</v>
+        <v>125017048</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514346</v>
+        <v>514295</v>
       </c>
       <c r="R2" t="n">
-        <v>6741714</v>
+        <v>6741934</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017081</v>
+        <v>125017032</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +789,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514370</v>
+        <v>514330</v>
       </c>
       <c r="R3" t="n">
-        <v>6742029</v>
+        <v>6741874</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017021</v>
+        <v>125017053</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514291</v>
+        <v>514273</v>
       </c>
       <c r="R4" t="n">
-        <v>6741927</v>
+        <v>6741841</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017014</v>
+        <v>125017069</v>
       </c>
       <c r="B5" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514311</v>
+        <v>514232</v>
       </c>
       <c r="R5" t="n">
-        <v>6741920</v>
+        <v>6741754</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017035</v>
+        <v>125017036</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,31 +1100,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1133,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514366</v>
+        <v>514293</v>
       </c>
       <c r="R6" t="n">
-        <v>6741941</v>
+        <v>6742097</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017027</v>
+        <v>125017037</v>
       </c>
       <c r="B7" t="n">
-        <v>96979</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1211,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514325</v>
+        <v>514291</v>
       </c>
       <c r="R7" t="n">
-        <v>6742071</v>
+        <v>6741924</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017036</v>
+        <v>125017047</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,47 +1313,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514293</v>
+        <v>514334</v>
       </c>
       <c r="R8" t="n">
-        <v>6742097</v>
+        <v>6741981</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017052</v>
+        <v>125017088</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,25 +1415,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1448,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514274</v>
+        <v>514339</v>
       </c>
       <c r="R9" t="n">
-        <v>6741848</v>
+        <v>6741763</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017042</v>
+        <v>125017034</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,38 +1517,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514331</v>
+        <v>514346</v>
       </c>
       <c r="R10" t="n">
-        <v>6742061</v>
+        <v>6741714</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,7 +1612,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017050</v>
+        <v>125017052</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514318</v>
+        <v>514274</v>
       </c>
       <c r="R11" t="n">
-        <v>6741915</v>
+        <v>6741848</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017041</v>
+        <v>125017071</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514235</v>
+        <v>514339</v>
       </c>
       <c r="R12" t="n">
-        <v>6742182</v>
+        <v>6741763</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,10 +1816,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017048</v>
+        <v>125017015</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1832,21 +1832,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514295</v>
+        <v>514225</v>
       </c>
       <c r="R13" t="n">
-        <v>6741934</v>
+        <v>6741799</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1892,6 +1892,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1918,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017015</v>
+        <v>125017084</v>
       </c>
       <c r="B14" t="n">
-        <v>96354</v>
+        <v>96227</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,25 +1935,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>2869</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1958,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514225</v>
+        <v>514370</v>
       </c>
       <c r="R14" t="n">
-        <v>6741799</v>
+        <v>6742063</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,11 +1999,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2025,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017037</v>
+        <v>125017085</v>
       </c>
       <c r="B15" t="n">
-        <v>91030</v>
+        <v>96227</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,25 +2037,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>2869</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514291</v>
+        <v>514342</v>
       </c>
       <c r="R15" t="n">
-        <v>6741924</v>
+        <v>6742146</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017078</v>
+        <v>125017033</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2139,38 +2139,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514359</v>
+        <v>514336</v>
       </c>
       <c r="R16" t="n">
-        <v>6742012</v>
+        <v>6741710</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,7 +2234,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017049</v>
+        <v>125017045</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2269,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514311</v>
+        <v>514340</v>
       </c>
       <c r="R17" t="n">
-        <v>6741920</v>
+        <v>6741996</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017031</v>
+        <v>125017016</v>
       </c>
       <c r="B18" t="n">
-        <v>8447</v>
+        <v>90977</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2347,39 +2352,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514358</v>
+        <v>514278</v>
       </c>
       <c r="R18" t="n">
-        <v>6741952</v>
+        <v>6741831</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125017086</v>
+        <v>125017031</v>
       </c>
       <c r="B19" t="n">
-        <v>5176</v>
+        <v>8447</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2454,34 +2454,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514306</v>
+        <v>514358</v>
       </c>
       <c r="R19" t="n">
-        <v>6741916</v>
+        <v>6741952</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,10 +2545,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125017025</v>
+        <v>125017044</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2556,21 +2561,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2580,10 +2585,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514390</v>
+        <v>514351</v>
       </c>
       <c r="R20" t="n">
-        <v>6741952</v>
+        <v>6742013</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,10 +2647,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125017071</v>
+        <v>125017087</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,25 +2659,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2682,10 +2687,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514339</v>
+        <v>514358</v>
       </c>
       <c r="R21" t="n">
-        <v>6741763</v>
+        <v>6742011</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2846,7 +2851,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125017072</v>
+        <v>125017074</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2886,10 +2891,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514411</v>
+        <v>514374</v>
       </c>
       <c r="R23" t="n">
-        <v>6741898</v>
+        <v>6741981</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,7 +2953,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125017055</v>
+        <v>125017070</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -2988,10 +2993,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514243</v>
+        <v>514333</v>
       </c>
       <c r="R24" t="n">
-        <v>6741837</v>
+        <v>6741764</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3050,10 +3055,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125017032</v>
+        <v>125017042</v>
       </c>
       <c r="B25" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3062,43 +3067,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514330</v>
+        <v>514331</v>
       </c>
       <c r="R25" t="n">
-        <v>6741874</v>
+        <v>6742061</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3157,7 +3157,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125017051</v>
+        <v>125017072</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514337</v>
+        <v>514411</v>
       </c>
       <c r="R26" t="n">
-        <v>6741897</v>
+        <v>6741898</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125017069</v>
+        <v>125017086</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3373,25 +3373,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514232</v>
+        <v>514306</v>
       </c>
       <c r="R28" t="n">
-        <v>6741754</v>
+        <v>6741916</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3463,10 +3463,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125017040</v>
+        <v>125017035</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3475,38 +3475,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514327</v>
+        <v>514366</v>
       </c>
       <c r="R29" t="n">
-        <v>6741885</v>
+        <v>6741941</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3539,11 +3544,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3570,10 +3570,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125017087</v>
+        <v>125017027</v>
       </c>
       <c r="B30" t="n">
-        <v>5176</v>
+        <v>96979</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3586,21 +3586,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514358</v>
+        <v>514325</v>
       </c>
       <c r="R30" t="n">
-        <v>6742011</v>
+        <v>6742071</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3672,10 +3672,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125017033</v>
+        <v>125017046</v>
       </c>
       <c r="B31" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3684,43 +3684,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514336</v>
+        <v>514337</v>
       </c>
       <c r="R31" t="n">
-        <v>6741710</v>
+        <v>6741991</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3779,7 +3774,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125017054</v>
+        <v>125017055</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3819,10 +3814,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514257</v>
+        <v>514243</v>
       </c>
       <c r="R32" t="n">
-        <v>6741839</v>
+        <v>6741837</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3881,10 +3876,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125017030</v>
+        <v>125017049</v>
       </c>
       <c r="B33" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3893,43 +3888,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514354</v>
+        <v>514311</v>
       </c>
       <c r="R33" t="n">
-        <v>6741952</v>
+        <v>6741920</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3988,10 +3978,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125017029</v>
+        <v>125017050</v>
       </c>
       <c r="B34" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4000,43 +3990,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514393</v>
+        <v>514318</v>
       </c>
       <c r="R34" t="n">
-        <v>6741939</v>
+        <v>6741915</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4095,10 +4080,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125017076</v>
+        <v>125017083</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4107,25 +4092,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4135,10 +4120,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514359</v>
+        <v>514373</v>
       </c>
       <c r="R35" t="n">
-        <v>6742010</v>
+        <v>6741951</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4197,10 +4182,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125017084</v>
+        <v>125017080</v>
       </c>
       <c r="B36" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4209,25 +4194,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4237,10 +4222,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514370</v>
+        <v>514363</v>
       </c>
       <c r="R36" t="n">
-        <v>6742063</v>
+        <v>6742014</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4299,10 +4284,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125017046</v>
+        <v>125017021</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4315,21 +4300,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4339,10 +4324,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514337</v>
+        <v>514291</v>
       </c>
       <c r="R37" t="n">
-        <v>6741991</v>
+        <v>6741927</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4401,10 +4386,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125017047</v>
+        <v>125017013</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4417,21 +4402,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4441,10 +4426,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514334</v>
+        <v>514345</v>
       </c>
       <c r="R38" t="n">
-        <v>6741981</v>
+        <v>6741942</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4503,7 +4488,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125017070</v>
+        <v>125017078</v>
       </c>
       <c r="B39" t="n">
         <v>78810</v>
@@ -4543,10 +4528,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514333</v>
+        <v>514359</v>
       </c>
       <c r="R39" t="n">
-        <v>6741764</v>
+        <v>6742012</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4605,10 +4590,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125017022</v>
+        <v>125017040</v>
       </c>
       <c r="B40" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4621,21 +4606,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4645,10 +4630,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514283</v>
+        <v>514327</v>
       </c>
       <c r="R40" t="n">
-        <v>6741836</v>
+        <v>6741885</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4681,6 +4666,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4707,7 +4697,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125017045</v>
+        <v>125017054</v>
       </c>
       <c r="B41" t="n">
         <v>78810</v>
@@ -4747,10 +4737,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514340</v>
+        <v>514257</v>
       </c>
       <c r="R41" t="n">
-        <v>6741996</v>
+        <v>6741839</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4809,10 +4799,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125017088</v>
+        <v>125017041</v>
       </c>
       <c r="B42" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4821,25 +4811,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4849,10 +4839,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514339</v>
+        <v>514235</v>
       </c>
       <c r="R42" t="n">
-        <v>6741763</v>
+        <v>6742182</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4911,10 +4901,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125017082</v>
+        <v>125017022</v>
       </c>
       <c r="B43" t="n">
-        <v>92293</v>
+        <v>91012</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4923,47 +4913,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514343</v>
+        <v>514283</v>
       </c>
       <c r="R43" t="n">
-        <v>6741717</v>
+        <v>6741836</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5022,10 +5003,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125017053</v>
+        <v>125017030</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5034,38 +5015,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514273</v>
+        <v>514354</v>
       </c>
       <c r="R44" t="n">
-        <v>6741841</v>
+        <v>6741952</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5124,10 +5110,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125017044</v>
+        <v>125017029</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5136,38 +5122,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514351</v>
+        <v>514393</v>
       </c>
       <c r="R45" t="n">
-        <v>6742013</v>
+        <v>6741939</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5226,10 +5217,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125017013</v>
+        <v>125017014</v>
       </c>
       <c r="B46" t="n">
-        <v>79428</v>
+        <v>74901</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5242,21 +5233,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5266,10 +5257,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514345</v>
+        <v>514311</v>
       </c>
       <c r="R46" t="n">
-        <v>6741942</v>
+        <v>6741920</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5328,10 +5319,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125017073</v>
+        <v>125017082</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5340,38 +5331,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514387</v>
+        <v>514343</v>
       </c>
       <c r="R47" t="n">
-        <v>6741982</v>
+        <v>6741717</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5430,10 +5430,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125017083</v>
+        <v>125017073</v>
       </c>
       <c r="B48" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5442,25 +5442,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514373</v>
+        <v>514387</v>
       </c>
       <c r="R48" t="n">
-        <v>6741951</v>
+        <v>6741982</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5532,7 +5532,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125017074</v>
+        <v>125017076</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -5572,10 +5572,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514374</v>
+        <v>514359</v>
       </c>
       <c r="R49" t="n">
-        <v>6741981</v>
+        <v>6742010</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5634,10 +5634,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125017085</v>
+        <v>125017025</v>
       </c>
       <c r="B50" t="n">
-        <v>96227</v>
+        <v>91012</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5646,25 +5646,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5674,10 +5674,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514342</v>
+        <v>514390</v>
       </c>
       <c r="R50" t="n">
-        <v>6742146</v>
+        <v>6741952</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5736,10 +5736,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125017016</v>
+        <v>125017081</v>
       </c>
       <c r="B51" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5748,25 +5748,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5776,10 +5776,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514278</v>
+        <v>514370</v>
       </c>
       <c r="R51" t="n">
-        <v>6741831</v>
+        <v>6742029</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5838,7 +5838,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125017080</v>
+        <v>125017051</v>
       </c>
       <c r="B52" t="n">
         <v>78810</v>
@@ -5878,10 +5878,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514363</v>
+        <v>514337</v>
       </c>
       <c r="R52" t="n">
-        <v>6742014</v>
+        <v>6741897</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 15392-2025 artfynd.xlsx
+++ b/artfynd/A 15392-2025 artfynd.xlsx
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017053</v>
+        <v>125017036</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,38 +896,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514273</v>
+        <v>514293</v>
       </c>
       <c r="R4" t="n">
-        <v>6741841</v>
+        <v>6742097</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +995,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017069</v>
+        <v>125017053</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1026,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514232</v>
+        <v>514273</v>
       </c>
       <c r="R5" t="n">
-        <v>6741754</v>
+        <v>6741841</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017036</v>
+        <v>125017069</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,47 +1109,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514293</v>
+        <v>514232</v>
       </c>
       <c r="R6" t="n">
-        <v>6742097</v>
+        <v>6741754</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1612,7 +1612,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017052</v>
+        <v>125017071</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514274</v>
+        <v>514339</v>
       </c>
       <c r="R11" t="n">
-        <v>6741848</v>
+        <v>6741763</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017071</v>
+        <v>125017052</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514339</v>
+        <v>514274</v>
       </c>
       <c r="R12" t="n">
-        <v>6741763</v>
+        <v>6741848</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,10 +1816,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017015</v>
+        <v>125017033</v>
       </c>
       <c r="B13" t="n">
-        <v>96354</v>
+        <v>8447</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,38 +1828,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514225</v>
+        <v>514336</v>
       </c>
       <c r="R13" t="n">
-        <v>6741799</v>
+        <v>6741710</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1892,11 +1897,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1923,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017084</v>
+        <v>125017015</v>
       </c>
       <c r="B14" t="n">
-        <v>96227</v>
+        <v>96354</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,25 +1935,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2869</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514370</v>
+        <v>514225</v>
       </c>
       <c r="R14" t="n">
-        <v>6742063</v>
+        <v>6741799</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,6 +1999,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2025,7 +2030,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017085</v>
+        <v>125017084</v>
       </c>
       <c r="B15" t="n">
         <v>96227</v>
@@ -2065,10 +2070,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514342</v>
+        <v>514370</v>
       </c>
       <c r="R15" t="n">
-        <v>6742146</v>
+        <v>6742063</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2127,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017033</v>
+        <v>125017085</v>
       </c>
       <c r="B16" t="n">
-        <v>8447</v>
+        <v>96227</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2143,39 +2148,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>2869</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514336</v>
+        <v>514342</v>
       </c>
       <c r="R16" t="n">
-        <v>6741710</v>
+        <v>6742146</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -3055,7 +3055,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125017042</v>
+        <v>125017072</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3095,10 +3095,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514331</v>
+        <v>514411</v>
       </c>
       <c r="R25" t="n">
-        <v>6742061</v>
+        <v>6741898</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3157,10 +3157,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125017072</v>
+        <v>125017086</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3169,25 +3169,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514411</v>
+        <v>514306</v>
       </c>
       <c r="R26" t="n">
-        <v>6741898</v>
+        <v>6741916</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3259,10 +3259,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125017075</v>
+        <v>125017035</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3271,38 +3271,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514356</v>
+        <v>514366</v>
       </c>
       <c r="R27" t="n">
-        <v>6742004</v>
+        <v>6741941</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3361,10 +3366,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125017086</v>
+        <v>125017027</v>
       </c>
       <c r="B28" t="n">
-        <v>5176</v>
+        <v>96979</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3377,21 +3382,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3401,10 +3406,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514306</v>
+        <v>514325</v>
       </c>
       <c r="R28" t="n">
-        <v>6741916</v>
+        <v>6742071</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3463,10 +3468,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125017035</v>
+        <v>125017042</v>
       </c>
       <c r="B29" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3475,43 +3480,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514366</v>
+        <v>514331</v>
       </c>
       <c r="R29" t="n">
-        <v>6741941</v>
+        <v>6742061</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3570,10 +3570,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125017027</v>
+        <v>125017075</v>
       </c>
       <c r="B30" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3582,25 +3582,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514325</v>
+        <v>514356</v>
       </c>
       <c r="R30" t="n">
-        <v>6742071</v>
+        <v>6742004</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3978,10 +3978,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125017050</v>
+        <v>125017083</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3990,25 +3990,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514318</v>
+        <v>514373</v>
       </c>
       <c r="R34" t="n">
-        <v>6741915</v>
+        <v>6741951</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4080,10 +4080,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125017083</v>
+        <v>125017080</v>
       </c>
       <c r="B35" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4092,25 +4092,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514373</v>
+        <v>514363</v>
       </c>
       <c r="R35" t="n">
-        <v>6741951</v>
+        <v>6742014</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125017080</v>
+        <v>125017050</v>
       </c>
       <c r="B36" t="n">
         <v>78810</v>
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514363</v>
+        <v>514318</v>
       </c>
       <c r="R36" t="n">
-        <v>6742014</v>
+        <v>6741915</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4697,10 +4697,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125017054</v>
+        <v>125017030</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4709,38 +4709,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514257</v>
+        <v>514354</v>
       </c>
       <c r="R41" t="n">
-        <v>6741839</v>
+        <v>6741952</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4799,10 +4804,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125017041</v>
+        <v>125017029</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4811,38 +4816,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514235</v>
+        <v>514393</v>
       </c>
       <c r="R42" t="n">
-        <v>6742182</v>
+        <v>6741939</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5003,10 +5013,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125017030</v>
+        <v>125017054</v>
       </c>
       <c r="B44" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5015,43 +5025,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514354</v>
+        <v>514257</v>
       </c>
       <c r="R44" t="n">
-        <v>6741952</v>
+        <v>6741839</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5110,10 +5115,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125017029</v>
+        <v>125017041</v>
       </c>
       <c r="B45" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5122,43 +5127,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514393</v>
+        <v>514235</v>
       </c>
       <c r="R45" t="n">
-        <v>6741939</v>
+        <v>6742182</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 15392-2025 artfynd.xlsx
+++ b/artfynd/A 15392-2025 artfynd.xlsx
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017036</v>
+        <v>125017053</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,47 +896,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514293</v>
+        <v>514273</v>
       </c>
       <c r="R4" t="n">
-        <v>6742097</v>
+        <v>6741841</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017053</v>
+        <v>125017069</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1035,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514273</v>
+        <v>514232</v>
       </c>
       <c r="R5" t="n">
-        <v>6741841</v>
+        <v>6741754</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017069</v>
+        <v>125017036</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,38 +1100,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514232</v>
+        <v>514293</v>
       </c>
       <c r="R6" t="n">
-        <v>6741754</v>
+        <v>6742097</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017045</v>
+        <v>125017016</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,25 +2246,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514340</v>
+        <v>514278</v>
       </c>
       <c r="R17" t="n">
-        <v>6741996</v>
+        <v>6741831</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017016</v>
+        <v>125017045</v>
       </c>
       <c r="B18" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,25 +2348,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514278</v>
+        <v>514340</v>
       </c>
       <c r="R18" t="n">
-        <v>6741831</v>
+        <v>6741996</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125017031</v>
+        <v>125017044</v>
       </c>
       <c r="B19" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,43 +2450,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514358</v>
+        <v>514351</v>
       </c>
       <c r="R19" t="n">
-        <v>6741952</v>
+        <v>6742013</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,10 +2540,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125017044</v>
+        <v>125017031</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2557,38 +2552,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514351</v>
+        <v>514358</v>
       </c>
       <c r="R20" t="n">
-        <v>6742013</v>
+        <v>6741952</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2647,10 +2647,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125017087</v>
+        <v>125017043</v>
       </c>
       <c r="B21" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2659,25 +2659,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2687,10 +2687,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514358</v>
+        <v>514354</v>
       </c>
       <c r="R21" t="n">
-        <v>6742011</v>
+        <v>6742044</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2749,7 +2749,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125017043</v>
+        <v>125017074</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2789,10 +2789,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514354</v>
+        <v>514374</v>
       </c>
       <c r="R22" t="n">
-        <v>6742044</v>
+        <v>6741981</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2851,7 +2851,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125017074</v>
+        <v>125017070</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514374</v>
+        <v>514333</v>
       </c>
       <c r="R23" t="n">
-        <v>6741981</v>
+        <v>6741764</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2953,10 +2953,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125017070</v>
+        <v>125017087</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2965,25 +2965,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514333</v>
+        <v>514358</v>
       </c>
       <c r="R24" t="n">
-        <v>6741764</v>
+        <v>6742011</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3055,7 +3055,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125017072</v>
+        <v>125017042</v>
       </c>
       <c r="B25" t="n">
         <v>78810</v>
@@ -3095,10 +3095,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514411</v>
+        <v>514331</v>
       </c>
       <c r="R25" t="n">
-        <v>6741898</v>
+        <v>6742061</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3157,10 +3157,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125017086</v>
+        <v>125017072</v>
       </c>
       <c r="B26" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3169,25 +3169,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514306</v>
+        <v>514411</v>
       </c>
       <c r="R26" t="n">
-        <v>6741916</v>
+        <v>6741898</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3259,10 +3259,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125017035</v>
+        <v>125017075</v>
       </c>
       <c r="B27" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3271,43 +3271,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514366</v>
+        <v>514356</v>
       </c>
       <c r="R27" t="n">
-        <v>6741941</v>
+        <v>6742004</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3366,10 +3361,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125017027</v>
+        <v>125017086</v>
       </c>
       <c r="B28" t="n">
-        <v>96979</v>
+        <v>5176</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3382,21 +3377,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3406,10 +3401,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514325</v>
+        <v>514306</v>
       </c>
       <c r="R28" t="n">
-        <v>6742071</v>
+        <v>6741916</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3468,10 +3463,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125017042</v>
+        <v>125017035</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3480,38 +3475,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514331</v>
+        <v>514366</v>
       </c>
       <c r="R29" t="n">
-        <v>6742061</v>
+        <v>6741941</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3570,10 +3570,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125017075</v>
+        <v>125017027</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>96979</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3582,25 +3582,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514356</v>
+        <v>514325</v>
       </c>
       <c r="R30" t="n">
-        <v>6742004</v>
+        <v>6742071</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3978,10 +3978,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125017083</v>
+        <v>125017050</v>
       </c>
       <c r="B34" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3990,25 +3990,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514373</v>
+        <v>514318</v>
       </c>
       <c r="R34" t="n">
-        <v>6741951</v>
+        <v>6741915</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4080,10 +4080,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125017080</v>
+        <v>125017083</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4092,25 +4092,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514363</v>
+        <v>514373</v>
       </c>
       <c r="R35" t="n">
-        <v>6742014</v>
+        <v>6741951</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125017050</v>
+        <v>125017080</v>
       </c>
       <c r="B36" t="n">
         <v>78810</v>
@@ -4222,10 +4222,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514318</v>
+        <v>514363</v>
       </c>
       <c r="R36" t="n">
-        <v>6741915</v>
+        <v>6742014</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4697,10 +4697,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125017030</v>
+        <v>125017054</v>
       </c>
       <c r="B41" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4709,43 +4709,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514354</v>
+        <v>514257</v>
       </c>
       <c r="R41" t="n">
-        <v>6741952</v>
+        <v>6741839</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4804,10 +4799,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125017029</v>
+        <v>125017041</v>
       </c>
       <c r="B42" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4816,43 +4811,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514393</v>
+        <v>514235</v>
       </c>
       <c r="R42" t="n">
-        <v>6741939</v>
+        <v>6742182</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5013,10 +5003,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125017054</v>
+        <v>125017030</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5025,38 +5015,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514257</v>
+        <v>514354</v>
       </c>
       <c r="R44" t="n">
-        <v>6741839</v>
+        <v>6741952</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5115,10 +5110,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125017041</v>
+        <v>125017029</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5127,38 +5122,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514235</v>
+        <v>514393</v>
       </c>
       <c r="R45" t="n">
-        <v>6742182</v>
+        <v>6741939</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 15392-2025 artfynd.xlsx
+++ b/artfynd/A 15392-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017048</v>
+        <v>125017082</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514295</v>
+        <v>514343</v>
       </c>
       <c r="R2" t="n">
-        <v>6741934</v>
+        <v>6741717</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017032</v>
+        <v>125017054</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,43 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514330</v>
+        <v>514257</v>
       </c>
       <c r="R3" t="n">
-        <v>6741874</v>
+        <v>6741839</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017053</v>
+        <v>125017029</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,38 +900,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514273</v>
+        <v>514393</v>
       </c>
       <c r="R4" t="n">
-        <v>6741841</v>
+        <v>6741939</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017069</v>
+        <v>125017034</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,38 +1007,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514232</v>
+        <v>514346</v>
       </c>
       <c r="R5" t="n">
-        <v>6741754</v>
+        <v>6741714</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017036</v>
+        <v>125017073</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,47 +1114,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514293</v>
+        <v>514387</v>
       </c>
       <c r="R6" t="n">
-        <v>6742097</v>
+        <v>6741982</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017037</v>
+        <v>125017045</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,21 +1220,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514291</v>
+        <v>514340</v>
       </c>
       <c r="R7" t="n">
-        <v>6741924</v>
+        <v>6741996</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017047</v>
+        <v>125017033</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,38 +1318,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514334</v>
+        <v>514336</v>
       </c>
       <c r="R8" t="n">
-        <v>6741981</v>
+        <v>6741710</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,10 +1413,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017088</v>
+        <v>125017035</v>
       </c>
       <c r="B9" t="n">
-        <v>5176</v>
+        <v>8447</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,34 +1429,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514339</v>
+        <v>514366</v>
       </c>
       <c r="R9" t="n">
-        <v>6741763</v>
+        <v>6741941</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017034</v>
+        <v>125017081</v>
       </c>
       <c r="B10" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,43 +1532,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514346</v>
+        <v>514370</v>
       </c>
       <c r="R10" t="n">
-        <v>6741714</v>
+        <v>6742029</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,7 +1622,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017071</v>
+        <v>125017080</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1652,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514339</v>
+        <v>514363</v>
       </c>
       <c r="R11" t="n">
-        <v>6741763</v>
+        <v>6742014</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,7 +1724,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017052</v>
+        <v>125017069</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1754,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514274</v>
+        <v>514232</v>
       </c>
       <c r="R12" t="n">
-        <v>6741848</v>
+        <v>6741754</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017033</v>
+        <v>125017076</v>
       </c>
       <c r="B13" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,43 +1838,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514336</v>
+        <v>514359</v>
       </c>
       <c r="R13" t="n">
-        <v>6741710</v>
+        <v>6742010</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017015</v>
+        <v>125017084</v>
       </c>
       <c r="B14" t="n">
-        <v>96354</v>
+        <v>96227</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,25 +1940,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>2869</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1963,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514225</v>
+        <v>514370</v>
       </c>
       <c r="R14" t="n">
-        <v>6741799</v>
+        <v>6742063</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,11 +2004,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2030,10 +2030,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017084</v>
+        <v>125017048</v>
       </c>
       <c r="B15" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,25 +2042,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514370</v>
+        <v>514295</v>
       </c>
       <c r="R15" t="n">
-        <v>6742063</v>
+        <v>6741934</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017085</v>
+        <v>125017044</v>
       </c>
       <c r="B16" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,25 +2144,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514342</v>
+        <v>514351</v>
       </c>
       <c r="R16" t="n">
-        <v>6742146</v>
+        <v>6742013</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,10 +2234,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017016</v>
+        <v>125017042</v>
       </c>
       <c r="B17" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,25 +2246,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514278</v>
+        <v>514331</v>
       </c>
       <c r="R17" t="n">
-        <v>6741831</v>
+        <v>6742061</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017045</v>
+        <v>125017016</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,25 +2348,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514340</v>
+        <v>514278</v>
       </c>
       <c r="R18" t="n">
-        <v>6741996</v>
+        <v>6741831</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125017044</v>
+        <v>125017013</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2454,21 +2454,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514351</v>
+        <v>514345</v>
       </c>
       <c r="R19" t="n">
-        <v>6742013</v>
+        <v>6741942</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,10 +2540,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125017031</v>
+        <v>125017027</v>
       </c>
       <c r="B20" t="n">
-        <v>8447</v>
+        <v>96979</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2556,39 +2556,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514358</v>
+        <v>514325</v>
       </c>
       <c r="R20" t="n">
-        <v>6741952</v>
+        <v>6742071</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2647,10 +2642,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125017043</v>
+        <v>125017021</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2663,21 +2658,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2687,10 +2682,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514354</v>
+        <v>514291</v>
       </c>
       <c r="R21" t="n">
-        <v>6742044</v>
+        <v>6741927</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2749,7 +2744,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125017074</v>
+        <v>125017041</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2789,10 +2784,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514374</v>
+        <v>514235</v>
       </c>
       <c r="R22" t="n">
-        <v>6741981</v>
+        <v>6742182</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2851,10 +2846,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125017070</v>
+        <v>125017086</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2863,25 +2858,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2891,10 +2886,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514333</v>
+        <v>514306</v>
       </c>
       <c r="R23" t="n">
-        <v>6741764</v>
+        <v>6741916</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2953,10 +2948,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125017087</v>
+        <v>125017075</v>
       </c>
       <c r="B24" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2965,25 +2960,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2993,10 +2988,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514358</v>
+        <v>514356</v>
       </c>
       <c r="R24" t="n">
-        <v>6742011</v>
+        <v>6742004</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3055,10 +3050,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125017042</v>
+        <v>125017083</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3067,25 +3062,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3095,10 +3090,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514331</v>
+        <v>514373</v>
       </c>
       <c r="R25" t="n">
-        <v>6742061</v>
+        <v>6741951</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3157,7 +3152,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125017072</v>
+        <v>125017078</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3197,10 +3192,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514411</v>
+        <v>514359</v>
       </c>
       <c r="R26" t="n">
-        <v>6741898</v>
+        <v>6742012</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3259,7 +3254,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125017075</v>
+        <v>125017051</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3299,10 +3294,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514356</v>
+        <v>514337</v>
       </c>
       <c r="R27" t="n">
-        <v>6742004</v>
+        <v>6741897</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3361,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125017086</v>
+        <v>125017025</v>
       </c>
       <c r="B28" t="n">
-        <v>5176</v>
+        <v>91012</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3373,25 +3368,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3401,10 +3396,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514306</v>
+        <v>514390</v>
       </c>
       <c r="R28" t="n">
-        <v>6741916</v>
+        <v>6741952</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3463,10 +3458,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125017035</v>
+        <v>125017050</v>
       </c>
       <c r="B29" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3475,43 +3470,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514366</v>
+        <v>514318</v>
       </c>
       <c r="R29" t="n">
-        <v>6741941</v>
+        <v>6741915</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3570,10 +3560,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125017027</v>
+        <v>125017074</v>
       </c>
       <c r="B30" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3582,25 +3572,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3610,10 +3600,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514325</v>
+        <v>514374</v>
       </c>
       <c r="R30" t="n">
-        <v>6742071</v>
+        <v>6741981</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3672,7 +3662,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125017046</v>
+        <v>125017043</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3712,10 +3702,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514337</v>
+        <v>514354</v>
       </c>
       <c r="R31" t="n">
-        <v>6741991</v>
+        <v>6742044</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3774,10 +3764,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125017055</v>
+        <v>125017015</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3790,21 +3780,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3814,10 +3804,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514243</v>
+        <v>514225</v>
       </c>
       <c r="R32" t="n">
-        <v>6741837</v>
+        <v>6741799</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3850,6 +3840,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3876,7 +3871,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125017049</v>
+        <v>125017046</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -3916,10 +3911,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514311</v>
+        <v>514337</v>
       </c>
       <c r="R33" t="n">
-        <v>6741920</v>
+        <v>6741991</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3978,10 +3973,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125017050</v>
+        <v>125017087</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3990,25 +3985,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4018,10 +4013,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514318</v>
+        <v>514358</v>
       </c>
       <c r="R34" t="n">
-        <v>6741915</v>
+        <v>6742011</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4080,10 +4075,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125017083</v>
+        <v>125017088</v>
       </c>
       <c r="B35" t="n">
-        <v>96227</v>
+        <v>5176</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4096,21 +4091,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2869</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4120,10 +4115,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514373</v>
+        <v>514339</v>
       </c>
       <c r="R35" t="n">
-        <v>6741951</v>
+        <v>6741763</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4182,10 +4177,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125017080</v>
+        <v>125017030</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4194,38 +4189,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514363</v>
+        <v>514354</v>
       </c>
       <c r="R36" t="n">
-        <v>6742014</v>
+        <v>6741952</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4284,10 +4284,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125017021</v>
+        <v>125017052</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4300,21 +4300,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4324,10 +4324,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514291</v>
+        <v>514274</v>
       </c>
       <c r="R37" t="n">
-        <v>6741927</v>
+        <v>6741848</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4386,10 +4386,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125017013</v>
+        <v>125017022</v>
       </c>
       <c r="B38" t="n">
-        <v>79428</v>
+        <v>91012</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4402,21 +4402,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514345</v>
+        <v>514283</v>
       </c>
       <c r="R38" t="n">
-        <v>6741942</v>
+        <v>6741836</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4488,10 +4488,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125017078</v>
+        <v>125017085</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4500,25 +4500,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4528,10 +4528,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514359</v>
+        <v>514342</v>
       </c>
       <c r="R39" t="n">
-        <v>6742012</v>
+        <v>6742146</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4590,10 +4590,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125017040</v>
+        <v>125017014</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4606,21 +4606,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4630,10 +4630,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514327</v>
+        <v>514311</v>
       </c>
       <c r="R40" t="n">
-        <v>6741885</v>
+        <v>6741920</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4666,11 +4666,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4697,7 +4692,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125017054</v>
+        <v>125017070</v>
       </c>
       <c r="B41" t="n">
         <v>78810</v>
@@ -4737,10 +4732,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514257</v>
+        <v>514333</v>
       </c>
       <c r="R41" t="n">
-        <v>6741839</v>
+        <v>6741764</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4799,10 +4794,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125017041</v>
+        <v>125017037</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4815,21 +4810,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4839,10 +4834,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514235</v>
+        <v>514291</v>
       </c>
       <c r="R42" t="n">
-        <v>6742182</v>
+        <v>6741924</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4901,10 +4896,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125017022</v>
+        <v>125017031</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>8447</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4913,38 +4908,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514283</v>
+        <v>514358</v>
       </c>
       <c r="R43" t="n">
-        <v>6741836</v>
+        <v>6741952</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5003,10 +5003,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125017030</v>
+        <v>125017049</v>
       </c>
       <c r="B44" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5015,43 +5015,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514354</v>
+        <v>514311</v>
       </c>
       <c r="R44" t="n">
-        <v>6741952</v>
+        <v>6741920</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5110,10 +5105,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125017029</v>
+        <v>125017040</v>
       </c>
       <c r="B45" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5122,43 +5117,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514393</v>
+        <v>514327</v>
       </c>
       <c r="R45" t="n">
-        <v>6741939</v>
+        <v>6741885</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5191,6 +5181,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5217,10 +5212,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125017014</v>
+        <v>125017053</v>
       </c>
       <c r="B46" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5233,21 +5228,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5257,10 +5252,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514311</v>
+        <v>514273</v>
       </c>
       <c r="R46" t="n">
-        <v>6741920</v>
+        <v>6741841</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5319,10 +5314,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125017082</v>
+        <v>125017072</v>
       </c>
       <c r="B47" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5331,47 +5326,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514343</v>
+        <v>514411</v>
       </c>
       <c r="R47" t="n">
-        <v>6741717</v>
+        <v>6741898</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5430,7 +5416,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125017073</v>
+        <v>125017055</v>
       </c>
       <c r="B48" t="n">
         <v>78810</v>
@@ -5470,10 +5456,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514387</v>
+        <v>514243</v>
       </c>
       <c r="R48" t="n">
-        <v>6741982</v>
+        <v>6741837</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5532,7 +5518,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125017076</v>
+        <v>125017047</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -5572,10 +5558,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514359</v>
+        <v>514334</v>
       </c>
       <c r="R49" t="n">
-        <v>6742010</v>
+        <v>6741981</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5634,10 +5620,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125017025</v>
+        <v>125017032</v>
       </c>
       <c r="B50" t="n">
-        <v>91012</v>
+        <v>8447</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5646,38 +5632,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514390</v>
+        <v>514330</v>
       </c>
       <c r="R50" t="n">
-        <v>6741952</v>
+        <v>6741874</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5736,10 +5727,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125017081</v>
+        <v>125017036</v>
       </c>
       <c r="B51" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5748,38 +5739,47 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514370</v>
+        <v>514293</v>
       </c>
       <c r="R51" t="n">
-        <v>6742029</v>
+        <v>6742097</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5838,7 +5838,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125017051</v>
+        <v>125017071</v>
       </c>
       <c r="B52" t="n">
         <v>78810</v>
@@ -5878,10 +5878,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514337</v>
+        <v>514339</v>
       </c>
       <c r="R52" t="n">
-        <v>6741897</v>
+        <v>6741763</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 15392-2025 artfynd.xlsx
+++ b/artfynd/A 15392-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017082</v>
+        <v>125017016</v>
       </c>
       <c r="B2" t="n">
-        <v>92293</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514343</v>
+        <v>514278</v>
       </c>
       <c r="R2" t="n">
-        <v>6741717</v>
+        <v>6741831</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017054</v>
+        <v>125017086</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514257</v>
+        <v>514306</v>
       </c>
       <c r="R3" t="n">
-        <v>6741839</v>
+        <v>6741916</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017029</v>
+        <v>125017022</v>
       </c>
       <c r="B4" t="n">
-        <v>8447</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,43 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514393</v>
+        <v>514283</v>
       </c>
       <c r="R4" t="n">
-        <v>6741939</v>
+        <v>6741836</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017034</v>
+        <v>125017043</v>
       </c>
       <c r="B5" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,43 +993,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514346</v>
+        <v>514354</v>
       </c>
       <c r="R5" t="n">
-        <v>6741714</v>
+        <v>6742044</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017073</v>
+        <v>125017030</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,38 +1095,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514387</v>
+        <v>514354</v>
       </c>
       <c r="R6" t="n">
-        <v>6741982</v>
+        <v>6741952</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017045</v>
+        <v>125017027</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>96979</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1244,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514340</v>
+        <v>514325</v>
       </c>
       <c r="R7" t="n">
-        <v>6741996</v>
+        <v>6742071</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017033</v>
+        <v>125017044</v>
       </c>
       <c r="B8" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,43 +1304,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514336</v>
+        <v>514351</v>
       </c>
       <c r="R8" t="n">
-        <v>6741710</v>
+        <v>6742013</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017035</v>
+        <v>125017081</v>
       </c>
       <c r="B9" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,43 +1406,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514366</v>
+        <v>514370</v>
       </c>
       <c r="R9" t="n">
-        <v>6741941</v>
+        <v>6742029</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1520,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017081</v>
+        <v>125017071</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1560,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514370</v>
+        <v>514339</v>
       </c>
       <c r="R10" t="n">
-        <v>6742029</v>
+        <v>6741763</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017080</v>
+        <v>125017084</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,25 +1610,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1662,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514363</v>
+        <v>514370</v>
       </c>
       <c r="R11" t="n">
-        <v>6742014</v>
+        <v>6742063</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017069</v>
+        <v>125017085</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1764,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514232</v>
+        <v>514342</v>
       </c>
       <c r="R12" t="n">
-        <v>6741754</v>
+        <v>6742146</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,7 +1802,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017076</v>
+        <v>125017051</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1866,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514359</v>
+        <v>514337</v>
       </c>
       <c r="R13" t="n">
-        <v>6742010</v>
+        <v>6741897</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017084</v>
+        <v>125017047</v>
       </c>
       <c r="B14" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,25 +1916,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1968,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514370</v>
+        <v>514334</v>
       </c>
       <c r="R14" t="n">
-        <v>6742063</v>
+        <v>6741981</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017048</v>
+        <v>125017013</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2046,21 +2022,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2070,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514295</v>
+        <v>514345</v>
       </c>
       <c r="R15" t="n">
-        <v>6741934</v>
+        <v>6741942</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,7 +2108,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017044</v>
+        <v>125017069</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2172,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514351</v>
+        <v>514232</v>
       </c>
       <c r="R16" t="n">
-        <v>6742013</v>
+        <v>6741754</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017042</v>
+        <v>125017082</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,38 +2222,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514331</v>
+        <v>514343</v>
       </c>
       <c r="R17" t="n">
-        <v>6742061</v>
+        <v>6741717</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017016</v>
+        <v>125017036</v>
       </c>
       <c r="B18" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,38 +2333,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514278</v>
+        <v>514293</v>
       </c>
       <c r="R18" t="n">
-        <v>6741831</v>
+        <v>6742097</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,10 +2432,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125017013</v>
+        <v>125017033</v>
       </c>
       <c r="B19" t="n">
-        <v>79428</v>
+        <v>8447</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,38 +2444,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514345</v>
+        <v>514336</v>
       </c>
       <c r="R19" t="n">
-        <v>6741942</v>
+        <v>6741710</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,10 +2539,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125017027</v>
+        <v>125017054</v>
       </c>
       <c r="B20" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,25 +2551,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2580,10 +2579,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514325</v>
+        <v>514257</v>
       </c>
       <c r="R20" t="n">
-        <v>6742071</v>
+        <v>6741839</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,10 +2641,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125017021</v>
+        <v>125017049</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2658,21 +2657,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2682,10 +2681,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514291</v>
+        <v>514311</v>
       </c>
       <c r="R21" t="n">
-        <v>6741927</v>
+        <v>6741920</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,7 +2743,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125017041</v>
+        <v>125017070</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2784,10 +2783,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514235</v>
+        <v>514333</v>
       </c>
       <c r="R22" t="n">
-        <v>6742182</v>
+        <v>6741764</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,7 +2845,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125017086</v>
+        <v>125017087</v>
       </c>
       <c r="B23" t="n">
         <v>5176</v>
@@ -2886,10 +2885,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514306</v>
+        <v>514358</v>
       </c>
       <c r="R23" t="n">
-        <v>6741916</v>
+        <v>6742011</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,7 +2947,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125017075</v>
+        <v>125017042</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -2988,10 +2987,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514356</v>
+        <v>514331</v>
       </c>
       <c r="R24" t="n">
-        <v>6742004</v>
+        <v>6742061</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3050,10 +3049,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125017083</v>
+        <v>125017041</v>
       </c>
       <c r="B25" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3062,25 +3061,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3090,10 +3089,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514373</v>
+        <v>514235</v>
       </c>
       <c r="R25" t="n">
-        <v>6741951</v>
+        <v>6742182</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,10 +3151,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125017078</v>
+        <v>125017021</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3168,21 +3167,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3192,10 +3191,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514359</v>
+        <v>514291</v>
       </c>
       <c r="R26" t="n">
-        <v>6742012</v>
+        <v>6741927</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3254,10 +3253,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125017051</v>
+        <v>125017014</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3270,21 +3269,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3294,10 +3293,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514337</v>
+        <v>514311</v>
       </c>
       <c r="R27" t="n">
-        <v>6741897</v>
+        <v>6741920</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3356,10 +3355,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125017025</v>
+        <v>125017088</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>5176</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3368,25 +3367,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3396,10 +3395,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514390</v>
+        <v>514339</v>
       </c>
       <c r="R28" t="n">
-        <v>6741952</v>
+        <v>6741763</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3458,10 +3457,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125017050</v>
+        <v>125017025</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3474,21 +3473,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3498,10 +3497,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514318</v>
+        <v>514390</v>
       </c>
       <c r="R29" t="n">
-        <v>6741915</v>
+        <v>6741952</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3560,7 +3559,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125017074</v>
+        <v>125017075</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3600,10 +3599,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514374</v>
+        <v>514356</v>
       </c>
       <c r="R30" t="n">
-        <v>6741981</v>
+        <v>6742004</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3662,10 +3661,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125017043</v>
+        <v>125017015</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3678,21 +3677,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3702,10 +3701,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514354</v>
+        <v>514225</v>
       </c>
       <c r="R31" t="n">
-        <v>6742044</v>
+        <v>6741799</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3738,6 +3737,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3764,10 +3768,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125017015</v>
+        <v>125017078</v>
       </c>
       <c r="B32" t="n">
-        <v>96354</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3780,21 +3784,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3804,10 +3808,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514225</v>
+        <v>514359</v>
       </c>
       <c r="R32" t="n">
-        <v>6741799</v>
+        <v>6742012</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3840,11 +3844,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3871,7 +3870,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125017046</v>
+        <v>125017074</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -3911,10 +3910,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514337</v>
+        <v>514374</v>
       </c>
       <c r="R33" t="n">
-        <v>6741991</v>
+        <v>6741981</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3973,10 +3972,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125017087</v>
+        <v>125017032</v>
       </c>
       <c r="B34" t="n">
-        <v>5176</v>
+        <v>8447</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3989,34 +3988,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514358</v>
+        <v>514330</v>
       </c>
       <c r="R34" t="n">
-        <v>6742011</v>
+        <v>6741874</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4075,10 +4079,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125017088</v>
+        <v>125017031</v>
       </c>
       <c r="B35" t="n">
-        <v>5176</v>
+        <v>8447</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4091,34 +4095,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514339</v>
+        <v>514358</v>
       </c>
       <c r="R35" t="n">
-        <v>6741763</v>
+        <v>6741952</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4177,10 +4186,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125017030</v>
+        <v>125017076</v>
       </c>
       <c r="B36" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4189,43 +4198,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514354</v>
+        <v>514359</v>
       </c>
       <c r="R36" t="n">
-        <v>6741952</v>
+        <v>6742010</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4284,7 +4288,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125017052</v>
+        <v>125017053</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4324,10 +4328,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514274</v>
+        <v>514273</v>
       </c>
       <c r="R37" t="n">
-        <v>6741848</v>
+        <v>6741841</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4386,10 +4390,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125017022</v>
+        <v>125017055</v>
       </c>
       <c r="B38" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4402,21 +4406,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4426,10 +4430,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514283</v>
+        <v>514243</v>
       </c>
       <c r="R38" t="n">
-        <v>6741836</v>
+        <v>6741837</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4488,10 +4492,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125017085</v>
+        <v>125017040</v>
       </c>
       <c r="B39" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4500,25 +4504,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4528,10 +4532,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514342</v>
+        <v>514327</v>
       </c>
       <c r="R39" t="n">
-        <v>6742146</v>
+        <v>6741885</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4564,6 +4568,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4590,10 +4599,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125017014</v>
+        <v>125017052</v>
       </c>
       <c r="B40" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4606,21 +4615,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4630,10 +4639,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514311</v>
+        <v>514274</v>
       </c>
       <c r="R40" t="n">
-        <v>6741920</v>
+        <v>6741848</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4692,7 +4701,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125017070</v>
+        <v>125017046</v>
       </c>
       <c r="B41" t="n">
         <v>78810</v>
@@ -4732,10 +4741,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514333</v>
+        <v>514337</v>
       </c>
       <c r="R41" t="n">
-        <v>6741764</v>
+        <v>6741991</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4794,10 +4803,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125017037</v>
+        <v>125017080</v>
       </c>
       <c r="B42" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4810,21 +4819,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4834,10 +4843,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514291</v>
+        <v>514363</v>
       </c>
       <c r="R42" t="n">
-        <v>6741924</v>
+        <v>6742014</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4896,10 +4905,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125017031</v>
+        <v>125017048</v>
       </c>
       <c r="B43" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4908,43 +4917,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514358</v>
+        <v>514295</v>
       </c>
       <c r="R43" t="n">
-        <v>6741952</v>
+        <v>6741934</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5003,10 +5007,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125017049</v>
+        <v>125017037</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5019,21 +5023,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5043,10 +5047,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514311</v>
+        <v>514291</v>
       </c>
       <c r="R44" t="n">
-        <v>6741920</v>
+        <v>6741924</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5105,7 +5109,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125017040</v>
+        <v>125017072</v>
       </c>
       <c r="B45" t="n">
         <v>78810</v>
@@ -5145,10 +5149,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514327</v>
+        <v>514411</v>
       </c>
       <c r="R45" t="n">
-        <v>6741885</v>
+        <v>6741898</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5181,11 +5185,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5212,7 +5211,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125017053</v>
+        <v>125017073</v>
       </c>
       <c r="B46" t="n">
         <v>78810</v>
@@ -5252,10 +5251,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514273</v>
+        <v>514387</v>
       </c>
       <c r="R46" t="n">
-        <v>6741841</v>
+        <v>6741982</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5314,7 +5313,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125017072</v>
+        <v>125017050</v>
       </c>
       <c r="B47" t="n">
         <v>78810</v>
@@ -5354,10 +5353,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514411</v>
+        <v>514318</v>
       </c>
       <c r="R47" t="n">
-        <v>6741898</v>
+        <v>6741915</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5416,7 +5415,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125017055</v>
+        <v>125017045</v>
       </c>
       <c r="B48" t="n">
         <v>78810</v>
@@ -5456,10 +5455,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514243</v>
+        <v>514340</v>
       </c>
       <c r="R48" t="n">
-        <v>6741837</v>
+        <v>6741996</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5518,10 +5517,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125017047</v>
+        <v>125017034</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5530,38 +5529,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514334</v>
+        <v>514346</v>
       </c>
       <c r="R49" t="n">
-        <v>6741981</v>
+        <v>6741714</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5620,7 +5624,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125017032</v>
+        <v>125017029</v>
       </c>
       <c r="B50" t="n">
         <v>8447</v>
@@ -5656,7 +5660,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5665,10 +5669,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514330</v>
+        <v>514393</v>
       </c>
       <c r="R50" t="n">
-        <v>6741874</v>
+        <v>6741939</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5727,10 +5731,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125017036</v>
+        <v>125017035</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5739,35 +5743,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5776,10 +5776,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514293</v>
+        <v>514366</v>
       </c>
       <c r="R51" t="n">
-        <v>6742097</v>
+        <v>6741941</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5838,10 +5838,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125017071</v>
+        <v>125017083</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5850,25 +5850,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5878,10 +5878,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514339</v>
+        <v>514373</v>
       </c>
       <c r="R52" t="n">
-        <v>6741763</v>
+        <v>6741951</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 15392-2025 artfynd.xlsx
+++ b/artfynd/A 15392-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017016</v>
+        <v>125017069</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514278</v>
+        <v>514232</v>
       </c>
       <c r="R2" t="n">
-        <v>6741831</v>
+        <v>6741754</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017086</v>
+        <v>125017075</v>
       </c>
       <c r="B3" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514306</v>
+        <v>514356</v>
       </c>
       <c r="R3" t="n">
-        <v>6741916</v>
+        <v>6742004</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017022</v>
+        <v>125017070</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514283</v>
+        <v>514333</v>
       </c>
       <c r="R4" t="n">
-        <v>6741836</v>
+        <v>6741764</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017043</v>
+        <v>125017041</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514354</v>
+        <v>514235</v>
       </c>
       <c r="R5" t="n">
-        <v>6742044</v>
+        <v>6742182</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017030</v>
+        <v>125017046</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,43 +1095,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514354</v>
+        <v>514337</v>
       </c>
       <c r="R6" t="n">
-        <v>6741952</v>
+        <v>6741991</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017027</v>
+        <v>125017086</v>
       </c>
       <c r="B7" t="n">
-        <v>96979</v>
+        <v>5176</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514325</v>
+        <v>514306</v>
       </c>
       <c r="R7" t="n">
-        <v>6742071</v>
+        <v>6741916</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017044</v>
+        <v>125017036</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,38 +1299,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514351</v>
+        <v>514293</v>
       </c>
       <c r="R8" t="n">
-        <v>6742013</v>
+        <v>6742097</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,7 +1398,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017081</v>
+        <v>125017055</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1434,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514370</v>
+        <v>514243</v>
       </c>
       <c r="R9" t="n">
-        <v>6742029</v>
+        <v>6741837</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,7 +1500,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017071</v>
+        <v>125017074</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1536,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514339</v>
+        <v>514374</v>
       </c>
       <c r="R10" t="n">
-        <v>6741763</v>
+        <v>6741981</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017084</v>
+        <v>125017015</v>
       </c>
       <c r="B11" t="n">
-        <v>96227</v>
+        <v>96354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,25 +1614,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2869</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514370</v>
+        <v>514225</v>
       </c>
       <c r="R11" t="n">
-        <v>6742063</v>
+        <v>6741799</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1674,6 +1678,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017085</v>
+        <v>125017022</v>
       </c>
       <c r="B12" t="n">
-        <v>96227</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1721,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514342</v>
+        <v>514283</v>
       </c>
       <c r="R12" t="n">
-        <v>6742146</v>
+        <v>6741836</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017051</v>
+        <v>125017025</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1827,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514337</v>
+        <v>514390</v>
       </c>
       <c r="R13" t="n">
-        <v>6741897</v>
+        <v>6741952</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1913,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017047</v>
+        <v>125017051</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1944,10 +1953,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514334</v>
+        <v>514337</v>
       </c>
       <c r="R14" t="n">
-        <v>6741981</v>
+        <v>6741897</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,10 +2015,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017013</v>
+        <v>125017087</v>
       </c>
       <c r="B15" t="n">
-        <v>79428</v>
+        <v>5176</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,25 +2027,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514345</v>
+        <v>514358</v>
       </c>
       <c r="R15" t="n">
-        <v>6741942</v>
+        <v>6742011</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017069</v>
+        <v>125017082</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>92293</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,38 +2129,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514232</v>
+        <v>514343</v>
       </c>
       <c r="R16" t="n">
-        <v>6741754</v>
+        <v>6741717</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,10 +2228,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017082</v>
+        <v>125017071</v>
       </c>
       <c r="B17" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,47 +2240,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514343</v>
+        <v>514339</v>
       </c>
       <c r="R17" t="n">
-        <v>6741717</v>
+        <v>6741763</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2321,10 +2330,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017036</v>
+        <v>125017085</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>96227</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,47 +2342,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514293</v>
+        <v>514342</v>
       </c>
       <c r="R18" t="n">
-        <v>6742097</v>
+        <v>6742146</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125017033</v>
+        <v>125017050</v>
       </c>
       <c r="B19" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2444,43 +2444,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514336</v>
+        <v>514318</v>
       </c>
       <c r="R19" t="n">
-        <v>6741710</v>
+        <v>6741915</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2641,10 +2636,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125017049</v>
+        <v>125017034</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2653,38 +2648,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514311</v>
+        <v>514346</v>
       </c>
       <c r="R21" t="n">
-        <v>6741920</v>
+        <v>6741714</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125017070</v>
+        <v>125017072</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514333</v>
+        <v>514411</v>
       </c>
       <c r="R22" t="n">
-        <v>6741764</v>
+        <v>6741898</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2845,10 +2845,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125017087</v>
+        <v>125017033</v>
       </c>
       <c r="B23" t="n">
-        <v>5176</v>
+        <v>8447</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2861,34 +2861,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514358</v>
+        <v>514336</v>
       </c>
       <c r="R23" t="n">
-        <v>6742011</v>
+        <v>6741710</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2947,10 +2952,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125017042</v>
+        <v>125017083</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2959,25 +2964,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2987,10 +2992,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514331</v>
+        <v>514373</v>
       </c>
       <c r="R24" t="n">
-        <v>6742061</v>
+        <v>6741951</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3049,10 +3054,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125017041</v>
+        <v>125017014</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3065,21 +3070,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3089,10 +3094,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514235</v>
+        <v>514311</v>
       </c>
       <c r="R25" t="n">
-        <v>6742182</v>
+        <v>6741920</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3151,10 +3156,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125017021</v>
+        <v>125017040</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3167,21 +3172,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3191,10 +3196,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514291</v>
+        <v>514327</v>
       </c>
       <c r="R26" t="n">
-        <v>6741927</v>
+        <v>6741885</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3227,6 +3232,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3253,10 +3263,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125017014</v>
+        <v>125017027</v>
       </c>
       <c r="B27" t="n">
-        <v>74901</v>
+        <v>96979</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3265,25 +3275,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3293,10 +3303,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514311</v>
+        <v>514325</v>
       </c>
       <c r="R27" t="n">
-        <v>6741920</v>
+        <v>6742071</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3355,10 +3365,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125017088</v>
+        <v>125017016</v>
       </c>
       <c r="B28" t="n">
-        <v>5176</v>
+        <v>90977</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3371,21 +3381,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3395,10 +3405,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514339</v>
+        <v>514278</v>
       </c>
       <c r="R28" t="n">
-        <v>6741763</v>
+        <v>6741831</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3457,10 +3467,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125017025</v>
+        <v>125017081</v>
       </c>
       <c r="B29" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3473,21 +3483,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3497,10 +3507,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514390</v>
+        <v>514370</v>
       </c>
       <c r="R29" t="n">
-        <v>6741952</v>
+        <v>6742029</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3559,10 +3569,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125017075</v>
+        <v>125017013</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3575,21 +3585,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3599,10 +3609,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514356</v>
+        <v>514345</v>
       </c>
       <c r="R30" t="n">
-        <v>6742004</v>
+        <v>6741942</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3661,10 +3671,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125017015</v>
+        <v>125017035</v>
       </c>
       <c r="B31" t="n">
-        <v>96354</v>
+        <v>8447</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3673,38 +3683,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514225</v>
+        <v>514366</v>
       </c>
       <c r="R31" t="n">
-        <v>6741799</v>
+        <v>6741941</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3737,11 +3752,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3768,7 +3778,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125017078</v>
+        <v>125017048</v>
       </c>
       <c r="B32" t="n">
         <v>78810</v>
@@ -3808,10 +3818,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514359</v>
+        <v>514295</v>
       </c>
       <c r="R32" t="n">
-        <v>6742012</v>
+        <v>6741934</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3870,7 +3880,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125017074</v>
+        <v>125017078</v>
       </c>
       <c r="B33" t="n">
         <v>78810</v>
@@ -3910,10 +3920,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514374</v>
+        <v>514359</v>
       </c>
       <c r="R33" t="n">
-        <v>6741981</v>
+        <v>6742012</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3972,10 +3982,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125017032</v>
+        <v>125017073</v>
       </c>
       <c r="B34" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3984,43 +3994,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514330</v>
+        <v>514387</v>
       </c>
       <c r="R34" t="n">
-        <v>6741874</v>
+        <v>6741982</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4079,10 +4084,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125017031</v>
+        <v>125017049</v>
       </c>
       <c r="B35" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4091,43 +4096,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514358</v>
+        <v>514311</v>
       </c>
       <c r="R35" t="n">
-        <v>6741952</v>
+        <v>6741920</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4186,10 +4186,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125017076</v>
+        <v>125017084</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4198,25 +4198,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4226,10 +4226,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514359</v>
+        <v>514370</v>
       </c>
       <c r="R36" t="n">
-        <v>6742010</v>
+        <v>6742063</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4390,7 +4390,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125017055</v>
+        <v>125017044</v>
       </c>
       <c r="B38" t="n">
         <v>78810</v>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514243</v>
+        <v>514351</v>
       </c>
       <c r="R38" t="n">
-        <v>6741837</v>
+        <v>6742013</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4492,10 +4492,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125017040</v>
+        <v>125017032</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4504,38 +4504,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514327</v>
+        <v>514330</v>
       </c>
       <c r="R39" t="n">
-        <v>6741885</v>
+        <v>6741874</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4568,11 +4573,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4599,10 +4599,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125017052</v>
+        <v>125017088</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4611,25 +4611,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4639,10 +4639,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514274</v>
+        <v>514339</v>
       </c>
       <c r="R40" t="n">
-        <v>6741848</v>
+        <v>6741763</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4701,7 +4701,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125017046</v>
+        <v>125017052</v>
       </c>
       <c r="B41" t="n">
         <v>78810</v>
@@ -4741,10 +4741,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514337</v>
+        <v>514274</v>
       </c>
       <c r="R41" t="n">
-        <v>6741991</v>
+        <v>6741848</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4803,7 +4803,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125017080</v>
+        <v>125017045</v>
       </c>
       <c r="B42" t="n">
         <v>78810</v>
@@ -4843,10 +4843,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514363</v>
+        <v>514340</v>
       </c>
       <c r="R42" t="n">
-        <v>6742014</v>
+        <v>6741996</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4905,7 +4905,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125017048</v>
+        <v>125017047</v>
       </c>
       <c r="B43" t="n">
         <v>78810</v>
@@ -4945,10 +4945,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514295</v>
+        <v>514334</v>
       </c>
       <c r="R43" t="n">
-        <v>6741934</v>
+        <v>6741981</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5007,10 +5007,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125017037</v>
+        <v>125017042</v>
       </c>
       <c r="B44" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5023,21 +5023,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5047,10 +5047,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514291</v>
+        <v>514331</v>
       </c>
       <c r="R44" t="n">
-        <v>6741924</v>
+        <v>6742061</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5109,10 +5109,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125017072</v>
+        <v>125017031</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5121,38 +5121,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514411</v>
+        <v>514358</v>
       </c>
       <c r="R45" t="n">
-        <v>6741898</v>
+        <v>6741952</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5211,10 +5216,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125017073</v>
+        <v>125017030</v>
       </c>
       <c r="B46" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5223,38 +5228,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514387</v>
+        <v>514354</v>
       </c>
       <c r="R46" t="n">
-        <v>6741982</v>
+        <v>6741952</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5313,10 +5323,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125017050</v>
+        <v>125017037</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5329,21 +5339,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5353,10 +5363,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514318</v>
+        <v>514291</v>
       </c>
       <c r="R47" t="n">
-        <v>6741915</v>
+        <v>6741924</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5415,7 +5425,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125017045</v>
+        <v>125017076</v>
       </c>
       <c r="B48" t="n">
         <v>78810</v>
@@ -5455,10 +5465,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514340</v>
+        <v>514359</v>
       </c>
       <c r="R48" t="n">
-        <v>6741996</v>
+        <v>6742010</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5517,10 +5527,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125017034</v>
+        <v>125017043</v>
       </c>
       <c r="B49" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5529,43 +5539,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514346</v>
+        <v>514354</v>
       </c>
       <c r="R49" t="n">
-        <v>6741714</v>
+        <v>6742044</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5624,10 +5629,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125017029</v>
+        <v>125017080</v>
       </c>
       <c r="B50" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5636,43 +5641,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514393</v>
+        <v>514363</v>
       </c>
       <c r="R50" t="n">
-        <v>6741939</v>
+        <v>6742014</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5731,10 +5731,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125017035</v>
+        <v>125017021</v>
       </c>
       <c r="B51" t="n">
-        <v>8447</v>
+        <v>91012</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5743,43 +5743,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514366</v>
+        <v>514291</v>
       </c>
       <c r="R51" t="n">
-        <v>6741941</v>
+        <v>6741927</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5838,10 +5833,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125017083</v>
+        <v>125017029</v>
       </c>
       <c r="B52" t="n">
-        <v>96227</v>
+        <v>8447</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5854,34 +5849,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2869</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514373</v>
+        <v>514393</v>
       </c>
       <c r="R52" t="n">
-        <v>6741951</v>
+        <v>6741939</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 15392-2025 artfynd.xlsx
+++ b/artfynd/A 15392-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017069</v>
+        <v>125017014</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514232</v>
+        <v>514311</v>
       </c>
       <c r="R2" t="n">
-        <v>6741754</v>
+        <v>6741920</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017075</v>
+        <v>125017027</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>96979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514356</v>
+        <v>514325</v>
       </c>
       <c r="R3" t="n">
-        <v>6742004</v>
+        <v>6742071</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017070</v>
+        <v>125017046</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514333</v>
+        <v>514337</v>
       </c>
       <c r="R4" t="n">
-        <v>6741764</v>
+        <v>6741991</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017041</v>
+        <v>125017072</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514235</v>
+        <v>514411</v>
       </c>
       <c r="R5" t="n">
-        <v>6742182</v>
+        <v>6741898</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017046</v>
+        <v>125017025</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514337</v>
+        <v>514390</v>
       </c>
       <c r="R6" t="n">
-        <v>6741991</v>
+        <v>6741952</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017086</v>
+        <v>125017042</v>
       </c>
       <c r="B7" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514306</v>
+        <v>514331</v>
       </c>
       <c r="R7" t="n">
-        <v>6741916</v>
+        <v>6742061</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017036</v>
+        <v>125017048</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,47 +1299,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514293</v>
+        <v>514295</v>
       </c>
       <c r="R8" t="n">
-        <v>6742097</v>
+        <v>6741934</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1398,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017055</v>
+        <v>125017080</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1438,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514243</v>
+        <v>514363</v>
       </c>
       <c r="R9" t="n">
-        <v>6741837</v>
+        <v>6742014</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017074</v>
+        <v>125017054</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1540,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514374</v>
+        <v>514257</v>
       </c>
       <c r="R10" t="n">
-        <v>6741981</v>
+        <v>6741839</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017015</v>
+        <v>125017036</v>
       </c>
       <c r="B11" t="n">
-        <v>96354</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,38 +1605,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514225</v>
+        <v>514293</v>
       </c>
       <c r="R11" t="n">
-        <v>6741799</v>
+        <v>6742097</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,11 +1678,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1709,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017022</v>
+        <v>125017043</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,21 +1720,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1749,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514283</v>
+        <v>514354</v>
       </c>
       <c r="R12" t="n">
-        <v>6741836</v>
+        <v>6742044</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017025</v>
+        <v>125017041</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1827,21 +1822,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1846,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514390</v>
+        <v>514235</v>
       </c>
       <c r="R13" t="n">
-        <v>6741952</v>
+        <v>6742182</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017051</v>
+        <v>125017031</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,38 +1920,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514337</v>
+        <v>514358</v>
       </c>
       <c r="R14" t="n">
-        <v>6741897</v>
+        <v>6741952</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,10 +2015,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017087</v>
+        <v>125017016</v>
       </c>
       <c r="B15" t="n">
-        <v>5176</v>
+        <v>90977</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2031,21 +2031,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514358</v>
+        <v>514278</v>
       </c>
       <c r="R15" t="n">
-        <v>6742011</v>
+        <v>6741831</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,10 +2117,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017082</v>
+        <v>125017071</v>
       </c>
       <c r="B16" t="n">
-        <v>92293</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,47 +2129,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514343</v>
+        <v>514339</v>
       </c>
       <c r="R16" t="n">
-        <v>6741717</v>
+        <v>6741763</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,7 +2219,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017071</v>
+        <v>125017069</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2268,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514339</v>
+        <v>514232</v>
       </c>
       <c r="R17" t="n">
-        <v>6741763</v>
+        <v>6741754</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,10 +2321,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017085</v>
+        <v>125017015</v>
       </c>
       <c r="B18" t="n">
-        <v>96227</v>
+        <v>96354</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2342,25 +2333,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2370,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514342</v>
+        <v>514225</v>
       </c>
       <c r="R18" t="n">
-        <v>6742146</v>
+        <v>6741799</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2406,6 +2397,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2432,10 +2428,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125017050</v>
+        <v>125017030</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2444,38 +2440,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514318</v>
+        <v>514354</v>
       </c>
       <c r="R19" t="n">
-        <v>6741915</v>
+        <v>6741952</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2534,7 +2535,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125017054</v>
+        <v>125017070</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2574,10 +2575,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514257</v>
+        <v>514333</v>
       </c>
       <c r="R20" t="n">
-        <v>6741839</v>
+        <v>6741764</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2636,10 +2637,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125017034</v>
+        <v>125017022</v>
       </c>
       <c r="B21" t="n">
-        <v>8447</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2648,43 +2649,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514346</v>
+        <v>514283</v>
       </c>
       <c r="R21" t="n">
-        <v>6741714</v>
+        <v>6741836</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2743,7 +2739,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125017072</v>
+        <v>125017073</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2783,10 +2779,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514411</v>
+        <v>514387</v>
       </c>
       <c r="R22" t="n">
-        <v>6741898</v>
+        <v>6741982</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2845,7 +2841,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125017033</v>
+        <v>125017034</v>
       </c>
       <c r="B23" t="n">
         <v>8447</v>
@@ -2890,10 +2886,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514336</v>
+        <v>514346</v>
       </c>
       <c r="R23" t="n">
-        <v>6741710</v>
+        <v>6741714</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2952,10 +2948,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125017083</v>
+        <v>125017052</v>
       </c>
       <c r="B24" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2964,25 +2960,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2992,10 +2988,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514373</v>
+        <v>514274</v>
       </c>
       <c r="R24" t="n">
-        <v>6741951</v>
+        <v>6741848</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3054,10 +3050,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125017014</v>
+        <v>125017055</v>
       </c>
       <c r="B25" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3070,21 +3066,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3094,10 +3090,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514311</v>
+        <v>514243</v>
       </c>
       <c r="R25" t="n">
-        <v>6741920</v>
+        <v>6741837</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3156,7 +3152,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125017040</v>
+        <v>125017078</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3196,10 +3192,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514327</v>
+        <v>514359</v>
       </c>
       <c r="R26" t="n">
-        <v>6741885</v>
+        <v>6742012</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3232,11 +3228,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3263,10 +3254,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125017027</v>
+        <v>125017033</v>
       </c>
       <c r="B27" t="n">
-        <v>96979</v>
+        <v>8447</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3279,34 +3270,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514325</v>
+        <v>514336</v>
       </c>
       <c r="R27" t="n">
-        <v>6742071</v>
+        <v>6741710</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3365,10 +3361,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125017016</v>
+        <v>125017021</v>
       </c>
       <c r="B28" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3377,25 +3373,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3405,10 +3401,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514278</v>
+        <v>514291</v>
       </c>
       <c r="R28" t="n">
-        <v>6741831</v>
+        <v>6741927</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3467,10 +3463,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125017081</v>
+        <v>125017088</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3479,25 +3475,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3507,10 +3503,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514370</v>
+        <v>514339</v>
       </c>
       <c r="R29" t="n">
-        <v>6742029</v>
+        <v>6741763</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3569,10 +3565,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125017013</v>
+        <v>125017035</v>
       </c>
       <c r="B30" t="n">
-        <v>79428</v>
+        <v>8447</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3581,38 +3577,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514345</v>
+        <v>514366</v>
       </c>
       <c r="R30" t="n">
-        <v>6741942</v>
+        <v>6741941</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3671,10 +3672,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125017035</v>
+        <v>125017047</v>
       </c>
       <c r="B31" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3683,43 +3684,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514366</v>
+        <v>514334</v>
       </c>
       <c r="R31" t="n">
-        <v>6741941</v>
+        <v>6741981</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3778,10 +3774,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125017048</v>
+        <v>125017029</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3790,38 +3786,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514295</v>
+        <v>514393</v>
       </c>
       <c r="R32" t="n">
-        <v>6741934</v>
+        <v>6741939</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3880,10 +3881,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125017078</v>
+        <v>125017032</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3892,38 +3893,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514359</v>
+        <v>514330</v>
       </c>
       <c r="R33" t="n">
-        <v>6742012</v>
+        <v>6741874</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3982,7 +3988,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125017073</v>
+        <v>125017074</v>
       </c>
       <c r="B34" t="n">
         <v>78810</v>
@@ -4022,10 +4028,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514387</v>
+        <v>514374</v>
       </c>
       <c r="R34" t="n">
-        <v>6741982</v>
+        <v>6741981</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4084,7 +4090,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125017049</v>
+        <v>125017081</v>
       </c>
       <c r="B35" t="n">
         <v>78810</v>
@@ -4124,10 +4130,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514311</v>
+        <v>514370</v>
       </c>
       <c r="R35" t="n">
-        <v>6741920</v>
+        <v>6742029</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4186,10 +4192,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125017084</v>
+        <v>125017044</v>
       </c>
       <c r="B36" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4198,25 +4204,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4226,10 +4232,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514370</v>
+        <v>514351</v>
       </c>
       <c r="R36" t="n">
-        <v>6742063</v>
+        <v>6742013</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4288,7 +4294,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125017053</v>
+        <v>125017040</v>
       </c>
       <c r="B37" t="n">
         <v>78810</v>
@@ -4328,10 +4334,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514273</v>
+        <v>514327</v>
       </c>
       <c r="R37" t="n">
-        <v>6741841</v>
+        <v>6741885</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4364,6 +4370,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4390,7 +4401,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125017044</v>
+        <v>125017045</v>
       </c>
       <c r="B38" t="n">
         <v>78810</v>
@@ -4430,10 +4441,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514351</v>
+        <v>514340</v>
       </c>
       <c r="R38" t="n">
-        <v>6742013</v>
+        <v>6741996</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4492,10 +4503,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125017032</v>
+        <v>125017075</v>
       </c>
       <c r="B39" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4504,43 +4515,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514330</v>
+        <v>514356</v>
       </c>
       <c r="R39" t="n">
-        <v>6741874</v>
+        <v>6742004</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4599,10 +4605,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125017088</v>
+        <v>125017085</v>
       </c>
       <c r="B40" t="n">
-        <v>5176</v>
+        <v>96227</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4615,21 +4621,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100526</v>
+        <v>2869</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4639,10 +4645,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514339</v>
+        <v>514342</v>
       </c>
       <c r="R40" t="n">
-        <v>6741763</v>
+        <v>6742146</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4701,10 +4707,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125017052</v>
+        <v>125017013</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>79428</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4717,21 +4723,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4741,10 +4747,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514274</v>
+        <v>514345</v>
       </c>
       <c r="R41" t="n">
-        <v>6741848</v>
+        <v>6741942</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4803,10 +4809,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125017045</v>
+        <v>125017087</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4815,25 +4821,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4843,10 +4849,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514340</v>
+        <v>514358</v>
       </c>
       <c r="R42" t="n">
-        <v>6741996</v>
+        <v>6742011</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4905,7 +4911,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125017047</v>
+        <v>125017049</v>
       </c>
       <c r="B43" t="n">
         <v>78810</v>
@@ -4945,10 +4951,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514334</v>
+        <v>514311</v>
       </c>
       <c r="R43" t="n">
-        <v>6741981</v>
+        <v>6741920</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5007,10 +5013,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125017042</v>
+        <v>125017083</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5019,25 +5025,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5047,10 +5053,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514331</v>
+        <v>514373</v>
       </c>
       <c r="R44" t="n">
-        <v>6742061</v>
+        <v>6741951</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5109,10 +5115,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125017031</v>
+        <v>125017053</v>
       </c>
       <c r="B45" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5121,43 +5127,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514358</v>
+        <v>514273</v>
       </c>
       <c r="R45" t="n">
-        <v>6741952</v>
+        <v>6741841</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5216,10 +5217,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125017030</v>
+        <v>125017037</v>
       </c>
       <c r="B46" t="n">
-        <v>8447</v>
+        <v>91030</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5228,43 +5229,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514354</v>
+        <v>514291</v>
       </c>
       <c r="R46" t="n">
-        <v>6741952</v>
+        <v>6741924</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5323,10 +5319,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125017037</v>
+        <v>125017051</v>
       </c>
       <c r="B47" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5339,21 +5335,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5363,10 +5359,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514291</v>
+        <v>514337</v>
       </c>
       <c r="R47" t="n">
-        <v>6741924</v>
+        <v>6741897</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5527,7 +5523,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125017043</v>
+        <v>125017050</v>
       </c>
       <c r="B49" t="n">
         <v>78810</v>
@@ -5567,10 +5563,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514354</v>
+        <v>514318</v>
       </c>
       <c r="R49" t="n">
-        <v>6742044</v>
+        <v>6741915</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5629,10 +5625,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125017080</v>
+        <v>125017084</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5641,25 +5637,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5669,10 +5665,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514363</v>
+        <v>514370</v>
       </c>
       <c r="R50" t="n">
-        <v>6742014</v>
+        <v>6742063</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5731,10 +5727,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125017021</v>
+        <v>125017082</v>
       </c>
       <c r="B51" t="n">
-        <v>91012</v>
+        <v>92293</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5743,38 +5739,47 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514291</v>
+        <v>514343</v>
       </c>
       <c r="R51" t="n">
-        <v>6741927</v>
+        <v>6741717</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5833,10 +5838,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125017029</v>
+        <v>125017086</v>
       </c>
       <c r="B52" t="n">
-        <v>8447</v>
+        <v>5176</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5849,39 +5854,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514393</v>
+        <v>514306</v>
       </c>
       <c r="R52" t="n">
-        <v>6741939</v>
+        <v>6741916</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 15392-2025 artfynd.xlsx
+++ b/artfynd/A 15392-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017014</v>
+        <v>125017027</v>
       </c>
       <c r="B2" t="n">
-        <v>74901</v>
+        <v>96979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514311</v>
+        <v>514325</v>
       </c>
       <c r="R2" t="n">
-        <v>6741920</v>
+        <v>6742071</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017027</v>
+        <v>125017014</v>
       </c>
       <c r="B3" t="n">
-        <v>96979</v>
+        <v>74901</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514325</v>
+        <v>514311</v>
       </c>
       <c r="R3" t="n">
-        <v>6742071</v>
+        <v>6741920</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -2428,10 +2428,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125017030</v>
+        <v>125017022</v>
       </c>
       <c r="B19" t="n">
-        <v>8447</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2440,43 +2440,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514354</v>
+        <v>514283</v>
       </c>
       <c r="R19" t="n">
-        <v>6741952</v>
+        <v>6741836</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2637,10 +2632,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125017022</v>
+        <v>125017030</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>8447</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2649,38 +2644,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514283</v>
+        <v>514354</v>
       </c>
       <c r="R21" t="n">
-        <v>6741836</v>
+        <v>6741952</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3361,10 +3361,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125017021</v>
+        <v>125017088</v>
       </c>
       <c r="B28" t="n">
-        <v>91012</v>
+        <v>5176</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3373,25 +3373,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514291</v>
+        <v>514339</v>
       </c>
       <c r="R28" t="n">
-        <v>6741927</v>
+        <v>6741763</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3463,10 +3463,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125017088</v>
+        <v>125017021</v>
       </c>
       <c r="B29" t="n">
-        <v>5176</v>
+        <v>91012</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3475,25 +3475,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514339</v>
+        <v>514291</v>
       </c>
       <c r="R29" t="n">
-        <v>6741763</v>
+        <v>6741927</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3881,10 +3881,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125017032</v>
+        <v>125017074</v>
       </c>
       <c r="B33" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3893,43 +3893,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514330</v>
+        <v>514374</v>
       </c>
       <c r="R33" t="n">
-        <v>6741874</v>
+        <v>6741981</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3988,10 +3983,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125017074</v>
+        <v>125017032</v>
       </c>
       <c r="B34" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4000,38 +3995,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514374</v>
+        <v>514330</v>
       </c>
       <c r="R34" t="n">
-        <v>6741981</v>
+        <v>6741874</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 15392-2025 artfynd.xlsx
+++ b/artfynd/A 15392-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017027</v>
+        <v>125017076</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514325</v>
+        <v>514359</v>
       </c>
       <c r="R2" t="n">
-        <v>6742071</v>
+        <v>6742010</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017014</v>
+        <v>125017051</v>
       </c>
       <c r="B3" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514311</v>
+        <v>514337</v>
       </c>
       <c r="R3" t="n">
-        <v>6741920</v>
+        <v>6741897</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017046</v>
+        <v>125017025</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514337</v>
+        <v>514390</v>
       </c>
       <c r="R4" t="n">
-        <v>6741991</v>
+        <v>6741952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017025</v>
+        <v>125017046</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514390</v>
+        <v>514337</v>
       </c>
       <c r="R6" t="n">
-        <v>6741952</v>
+        <v>6741991</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017042</v>
+        <v>125017041</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514331</v>
+        <v>514235</v>
       </c>
       <c r="R7" t="n">
-        <v>6742061</v>
+        <v>6742182</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017048</v>
+        <v>125017037</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514295</v>
+        <v>514291</v>
       </c>
       <c r="R8" t="n">
-        <v>6741934</v>
+        <v>6741924</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017080</v>
+        <v>125017050</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514363</v>
+        <v>514318</v>
       </c>
       <c r="R9" t="n">
-        <v>6742014</v>
+        <v>6741915</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017054</v>
+        <v>125017049</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514257</v>
+        <v>514311</v>
       </c>
       <c r="R10" t="n">
-        <v>6741839</v>
+        <v>6741920</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017036</v>
+        <v>125017040</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,47 +1605,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514293</v>
+        <v>514327</v>
       </c>
       <c r="R11" t="n">
-        <v>6742097</v>
+        <v>6741885</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1678,6 +1669,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1704,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017043</v>
+        <v>125017087</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1716,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1744,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514354</v>
+        <v>514358</v>
       </c>
       <c r="R12" t="n">
-        <v>6742044</v>
+        <v>6742011</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,7 +1802,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017041</v>
+        <v>125017073</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1846,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514235</v>
+        <v>514387</v>
       </c>
       <c r="R13" t="n">
-        <v>6742182</v>
+        <v>6741982</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,7 +1904,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017031</v>
+        <v>125017035</v>
       </c>
       <c r="B14" t="n">
         <v>8447</v>
@@ -1944,7 +1940,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1953,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514358</v>
+        <v>514366</v>
       </c>
       <c r="R14" t="n">
-        <v>6741952</v>
+        <v>6741941</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017016</v>
+        <v>125017048</v>
       </c>
       <c r="B15" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2027,25 +2023,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2055,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514278</v>
+        <v>514295</v>
       </c>
       <c r="R15" t="n">
-        <v>6741831</v>
+        <v>6741934</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017071</v>
+        <v>125017031</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,38 +2125,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514339</v>
+        <v>514358</v>
       </c>
       <c r="R16" t="n">
-        <v>6741763</v>
+        <v>6741952</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,7 +2220,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017069</v>
+        <v>125017042</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2259,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514232</v>
+        <v>514331</v>
       </c>
       <c r="R17" t="n">
-        <v>6741754</v>
+        <v>6742061</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2321,10 +2322,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017015</v>
+        <v>125017014</v>
       </c>
       <c r="B18" t="n">
-        <v>96354</v>
+        <v>74901</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2337,21 +2338,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2361,10 +2362,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514225</v>
+        <v>514311</v>
       </c>
       <c r="R18" t="n">
-        <v>6741799</v>
+        <v>6741920</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2397,11 +2398,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2428,10 +2424,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125017022</v>
+        <v>125017045</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2444,21 +2440,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2468,10 +2464,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514283</v>
+        <v>514340</v>
       </c>
       <c r="R19" t="n">
-        <v>6741836</v>
+        <v>6741996</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2530,10 +2526,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125017070</v>
+        <v>125017027</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>96979</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2542,25 +2538,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2570,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514333</v>
+        <v>514325</v>
       </c>
       <c r="R20" t="n">
-        <v>6741764</v>
+        <v>6742071</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2632,10 +2628,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125017030</v>
+        <v>125017053</v>
       </c>
       <c r="B21" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2644,43 +2640,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514354</v>
+        <v>514273</v>
       </c>
       <c r="R21" t="n">
-        <v>6741952</v>
+        <v>6741841</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2739,7 +2730,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125017073</v>
+        <v>125017054</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2779,10 +2770,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514387</v>
+        <v>514257</v>
       </c>
       <c r="R22" t="n">
-        <v>6741982</v>
+        <v>6741839</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2841,10 +2832,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125017034</v>
+        <v>125017013</v>
       </c>
       <c r="B23" t="n">
-        <v>8447</v>
+        <v>79428</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2853,43 +2844,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514346</v>
+        <v>514345</v>
       </c>
       <c r="R23" t="n">
-        <v>6741714</v>
+        <v>6741942</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,7 +2934,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125017052</v>
+        <v>125017074</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -2988,10 +2974,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514274</v>
+        <v>514374</v>
       </c>
       <c r="R24" t="n">
-        <v>6741848</v>
+        <v>6741981</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3050,10 +3036,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125017055</v>
+        <v>125017021</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3066,21 +3052,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3090,10 +3076,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514243</v>
+        <v>514291</v>
       </c>
       <c r="R25" t="n">
-        <v>6741837</v>
+        <v>6741927</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,10 +3138,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125017078</v>
+        <v>125017016</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3164,25 +3150,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3192,10 +3178,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514359</v>
+        <v>514278</v>
       </c>
       <c r="R26" t="n">
-        <v>6742012</v>
+        <v>6741831</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3254,10 +3240,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125017033</v>
+        <v>125017080</v>
       </c>
       <c r="B27" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,43 +3252,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514336</v>
+        <v>514363</v>
       </c>
       <c r="R27" t="n">
-        <v>6741710</v>
+        <v>6742014</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3361,10 +3342,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125017088</v>
+        <v>125017044</v>
       </c>
       <c r="B28" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3373,25 +3354,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3401,10 +3382,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514339</v>
+        <v>514351</v>
       </c>
       <c r="R28" t="n">
-        <v>6741763</v>
+        <v>6742013</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3463,10 +3444,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125017021</v>
+        <v>125017032</v>
       </c>
       <c r="B29" t="n">
-        <v>91012</v>
+        <v>8447</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3475,38 +3456,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514291</v>
+        <v>514330</v>
       </c>
       <c r="R29" t="n">
-        <v>6741927</v>
+        <v>6741874</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3565,10 +3551,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125017035</v>
+        <v>125017078</v>
       </c>
       <c r="B30" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3577,43 +3563,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514366</v>
+        <v>514359</v>
       </c>
       <c r="R30" t="n">
-        <v>6741941</v>
+        <v>6742012</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3672,7 +3653,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125017047</v>
+        <v>125017075</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -3712,10 +3693,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514334</v>
+        <v>514356</v>
       </c>
       <c r="R31" t="n">
-        <v>6741981</v>
+        <v>6742004</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3774,10 +3755,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125017029</v>
+        <v>125017070</v>
       </c>
       <c r="B32" t="n">
-        <v>8447</v>
+        <v>78810</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3786,43 +3767,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514393</v>
+        <v>514333</v>
       </c>
       <c r="R32" t="n">
-        <v>6741939</v>
+        <v>6741764</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3881,10 +3857,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125017074</v>
+        <v>125017034</v>
       </c>
       <c r="B33" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3893,38 +3869,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514374</v>
+        <v>514346</v>
       </c>
       <c r="R33" t="n">
-        <v>6741981</v>
+        <v>6741714</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3983,10 +3964,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125017032</v>
+        <v>125017082</v>
       </c>
       <c r="B34" t="n">
-        <v>8447</v>
+        <v>92293</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3999,27 +3980,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4028,10 +4013,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514330</v>
+        <v>514343</v>
       </c>
       <c r="R34" t="n">
-        <v>6741874</v>
+        <v>6741717</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4090,10 +4075,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125017081</v>
+        <v>125017015</v>
       </c>
       <c r="B35" t="n">
-        <v>78810</v>
+        <v>96354</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4106,21 +4091,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4130,10 +4115,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514370</v>
+        <v>514225</v>
       </c>
       <c r="R35" t="n">
-        <v>6742029</v>
+        <v>6741799</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4166,6 +4151,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4192,10 +4182,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125017044</v>
+        <v>125017084</v>
       </c>
       <c r="B36" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4204,25 +4194,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4232,10 +4222,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514351</v>
+        <v>514370</v>
       </c>
       <c r="R36" t="n">
-        <v>6742013</v>
+        <v>6742063</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4294,10 +4284,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125017040</v>
+        <v>125017085</v>
       </c>
       <c r="B37" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4306,25 +4296,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4334,10 +4324,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514327</v>
+        <v>514342</v>
       </c>
       <c r="R37" t="n">
-        <v>6741885</v>
+        <v>6742146</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4370,11 +4360,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4401,10 +4386,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125017045</v>
+        <v>125017029</v>
       </c>
       <c r="B38" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4413,38 +4398,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514340</v>
+        <v>514393</v>
       </c>
       <c r="R38" t="n">
-        <v>6741996</v>
+        <v>6741939</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4503,7 +4493,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125017075</v>
+        <v>125017081</v>
       </c>
       <c r="B39" t="n">
         <v>78810</v>
@@ -4543,10 +4533,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514356</v>
+        <v>514370</v>
       </c>
       <c r="R39" t="n">
-        <v>6742004</v>
+        <v>6742029</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4605,10 +4595,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125017085</v>
+        <v>125017043</v>
       </c>
       <c r="B40" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4617,25 +4607,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4645,10 +4635,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514342</v>
+        <v>514354</v>
       </c>
       <c r="R40" t="n">
-        <v>6742146</v>
+        <v>6742044</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4707,10 +4697,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125017013</v>
+        <v>125017047</v>
       </c>
       <c r="B41" t="n">
-        <v>79428</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4723,21 +4713,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4747,10 +4737,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514345</v>
+        <v>514334</v>
       </c>
       <c r="R41" t="n">
-        <v>6741942</v>
+        <v>6741981</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4809,10 +4799,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125017087</v>
+        <v>125017055</v>
       </c>
       <c r="B42" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4821,25 +4811,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4849,10 +4839,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514358</v>
+        <v>514243</v>
       </c>
       <c r="R42" t="n">
-        <v>6742011</v>
+        <v>6741837</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4911,7 +4901,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125017049</v>
+        <v>125017071</v>
       </c>
       <c r="B43" t="n">
         <v>78810</v>
@@ -4951,10 +4941,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514311</v>
+        <v>514339</v>
       </c>
       <c r="R43" t="n">
-        <v>6741920</v>
+        <v>6741763</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5013,10 +5003,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125017083</v>
+        <v>125017088</v>
       </c>
       <c r="B44" t="n">
-        <v>96227</v>
+        <v>5176</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5029,21 +5019,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2869</v>
+        <v>100526</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5053,10 +5043,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514373</v>
+        <v>514339</v>
       </c>
       <c r="R44" t="n">
-        <v>6741951</v>
+        <v>6741763</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5115,10 +5105,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125017053</v>
+        <v>125017036</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5127,38 +5117,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514273</v>
+        <v>514293</v>
       </c>
       <c r="R45" t="n">
-        <v>6741841</v>
+        <v>6742097</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5217,10 +5216,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125017037</v>
+        <v>125017022</v>
       </c>
       <c r="B46" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5233,21 +5232,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5257,10 +5256,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514291</v>
+        <v>514283</v>
       </c>
       <c r="R46" t="n">
-        <v>6741924</v>
+        <v>6741836</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5319,10 +5318,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125017051</v>
+        <v>125017083</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5331,25 +5330,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5359,10 +5358,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514337</v>
+        <v>514373</v>
       </c>
       <c r="R47" t="n">
-        <v>6741897</v>
+        <v>6741951</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5421,7 +5420,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125017076</v>
+        <v>125017052</v>
       </c>
       <c r="B48" t="n">
         <v>78810</v>
@@ -5461,10 +5460,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514359</v>
+        <v>514274</v>
       </c>
       <c r="R48" t="n">
-        <v>6742010</v>
+        <v>6741848</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5523,10 +5522,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125017050</v>
+        <v>125017030</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5535,38 +5534,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514318</v>
+        <v>514354</v>
       </c>
       <c r="R49" t="n">
-        <v>6741915</v>
+        <v>6741952</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5625,10 +5629,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125017084</v>
+        <v>125017086</v>
       </c>
       <c r="B50" t="n">
-        <v>96227</v>
+        <v>5176</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5641,21 +5645,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2869</v>
+        <v>100526</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5665,10 +5669,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514370</v>
+        <v>514306</v>
       </c>
       <c r="R50" t="n">
-        <v>6742063</v>
+        <v>6741916</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5727,10 +5731,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125017082</v>
+        <v>125017033</v>
       </c>
       <c r="B51" t="n">
-        <v>92293</v>
+        <v>8447</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5743,31 +5747,27 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5776,10 +5776,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514343</v>
+        <v>514336</v>
       </c>
       <c r="R51" t="n">
-        <v>6741717</v>
+        <v>6741710</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5838,10 +5838,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125017086</v>
+        <v>125017069</v>
       </c>
       <c r="B52" t="n">
-        <v>5176</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5850,25 +5850,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5878,10 +5878,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514306</v>
+        <v>514232</v>
       </c>
       <c r="R52" t="n">
-        <v>6741916</v>
+        <v>6741754</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 15392-2025 artfynd.xlsx
+++ b/artfynd/A 15392-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017076</v>
+        <v>125017051</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514359</v>
+        <v>514337</v>
       </c>
       <c r="R2" t="n">
-        <v>6742010</v>
+        <v>6741897</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017051</v>
+        <v>125017043</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514337</v>
+        <v>514354</v>
       </c>
       <c r="R3" t="n">
-        <v>6741897</v>
+        <v>6742044</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017025</v>
+        <v>125017041</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514390</v>
+        <v>514235</v>
       </c>
       <c r="R4" t="n">
-        <v>6741952</v>
+        <v>6742182</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017072</v>
+        <v>125017082</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>92448</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514411</v>
+        <v>514343</v>
       </c>
       <c r="R5" t="n">
-        <v>6741898</v>
+        <v>6741717</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017046</v>
+        <v>125017075</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514337</v>
+        <v>514356</v>
       </c>
       <c r="R6" t="n">
-        <v>6741991</v>
+        <v>6742004</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017041</v>
+        <v>125017035</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,38 +1206,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514235</v>
+        <v>514366</v>
       </c>
       <c r="R7" t="n">
-        <v>6742182</v>
+        <v>6741941</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017037</v>
+        <v>125017085</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>96395</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1313,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514291</v>
+        <v>514342</v>
       </c>
       <c r="R8" t="n">
-        <v>6741924</v>
+        <v>6742146</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017050</v>
+        <v>125017025</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91166</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514318</v>
+        <v>514390</v>
       </c>
       <c r="R9" t="n">
-        <v>6741915</v>
+        <v>6741952</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017049</v>
+        <v>125017033</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,38 +1517,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514311</v>
+        <v>514336</v>
       </c>
       <c r="R10" t="n">
-        <v>6741920</v>
+        <v>6741710</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017040</v>
+        <v>125017029</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1605,38 +1624,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514327</v>
+        <v>514393</v>
       </c>
       <c r="R11" t="n">
-        <v>6741885</v>
+        <v>6741939</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,11 +1693,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017087</v>
+        <v>125017015</v>
       </c>
       <c r="B12" t="n">
-        <v>5176</v>
+        <v>96522</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1731,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514358</v>
+        <v>514225</v>
       </c>
       <c r="R12" t="n">
-        <v>6742011</v>
+        <v>6741799</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,6 +1795,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017073</v>
+        <v>125017084</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>96395</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1838,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514387</v>
+        <v>514370</v>
       </c>
       <c r="R13" t="n">
-        <v>6741982</v>
+        <v>6742063</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017035</v>
+        <v>125017048</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>78947</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,43 +1940,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514366</v>
+        <v>514295</v>
       </c>
       <c r="R14" t="n">
-        <v>6741941</v>
+        <v>6741934</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,10 +2030,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017048</v>
+        <v>125017016</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>91131</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2023,25 +2042,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2070,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514295</v>
+        <v>514278</v>
       </c>
       <c r="R15" t="n">
-        <v>6741934</v>
+        <v>6741831</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017031</v>
+        <v>125017050</v>
       </c>
       <c r="B16" t="n">
-        <v>8447</v>
+        <v>78947</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2125,43 +2144,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514358</v>
+        <v>514318</v>
       </c>
       <c r="R16" t="n">
-        <v>6741952</v>
+        <v>6741915</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2234,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017042</v>
+        <v>125017088</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,25 +2246,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514331</v>
+        <v>514339</v>
       </c>
       <c r="R17" t="n">
-        <v>6742061</v>
+        <v>6741763</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2322,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017014</v>
+        <v>125017046</v>
       </c>
       <c r="B18" t="n">
-        <v>74901</v>
+        <v>78947</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2338,21 +2352,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2362,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514311</v>
+        <v>514337</v>
       </c>
       <c r="R18" t="n">
-        <v>6741920</v>
+        <v>6741991</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125017045</v>
+        <v>125017040</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2464,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514340</v>
+        <v>514327</v>
       </c>
       <c r="R19" t="n">
-        <v>6741996</v>
+        <v>6741885</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2500,6 +2514,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2526,10 +2545,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125017027</v>
+        <v>125017021</v>
       </c>
       <c r="B20" t="n">
-        <v>96979</v>
+        <v>91166</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2538,25 +2557,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2585,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514325</v>
+        <v>514291</v>
       </c>
       <c r="R20" t="n">
-        <v>6742071</v>
+        <v>6741927</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,10 +2647,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125017053</v>
+        <v>125017080</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2668,10 +2687,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514273</v>
+        <v>514363</v>
       </c>
       <c r="R21" t="n">
-        <v>6741841</v>
+        <v>6742014</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,10 +2749,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125017054</v>
+        <v>125017081</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2770,10 +2789,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514257</v>
+        <v>514370</v>
       </c>
       <c r="R22" t="n">
-        <v>6741839</v>
+        <v>6742029</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2832,10 +2851,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125017013</v>
+        <v>125017047</v>
       </c>
       <c r="B23" t="n">
-        <v>79428</v>
+        <v>78947</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2848,21 +2867,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2872,10 +2891,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514345</v>
+        <v>514334</v>
       </c>
       <c r="R23" t="n">
-        <v>6741942</v>
+        <v>6741981</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2934,10 +2953,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125017074</v>
+        <v>125017054</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2974,10 +2993,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514374</v>
+        <v>514257</v>
       </c>
       <c r="R24" t="n">
-        <v>6741981</v>
+        <v>6741839</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3036,10 +3055,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125017021</v>
+        <v>125017087</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>5176</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3048,25 +3067,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3076,10 +3095,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514291</v>
+        <v>514358</v>
       </c>
       <c r="R25" t="n">
-        <v>6741927</v>
+        <v>6742011</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3138,10 +3157,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125017016</v>
+        <v>125017034</v>
       </c>
       <c r="B26" t="n">
-        <v>90977</v>
+        <v>8447</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3154,34 +3173,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514278</v>
+        <v>514346</v>
       </c>
       <c r="R26" t="n">
-        <v>6741831</v>
+        <v>6741714</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3240,10 +3264,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125017080</v>
+        <v>125017030</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>8447</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3252,38 +3276,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514363</v>
+        <v>514354</v>
       </c>
       <c r="R27" t="n">
-        <v>6742014</v>
+        <v>6741952</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3342,10 +3371,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125017044</v>
+        <v>125017022</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>91166</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3358,21 +3387,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3382,10 +3411,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514351</v>
+        <v>514283</v>
       </c>
       <c r="R28" t="n">
-        <v>6742013</v>
+        <v>6741836</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3444,10 +3473,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125017032</v>
+        <v>125017072</v>
       </c>
       <c r="B29" t="n">
-        <v>8447</v>
+        <v>78947</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3456,43 +3485,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514330</v>
+        <v>514411</v>
       </c>
       <c r="R29" t="n">
-        <v>6741874</v>
+        <v>6741898</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,10 +3575,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125017078</v>
+        <v>125017070</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3591,10 +3615,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514359</v>
+        <v>514333</v>
       </c>
       <c r="R30" t="n">
-        <v>6742012</v>
+        <v>6741764</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3653,10 +3677,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125017075</v>
+        <v>125017049</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3693,10 +3717,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514356</v>
+        <v>514311</v>
       </c>
       <c r="R31" t="n">
-        <v>6742004</v>
+        <v>6741920</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3755,10 +3779,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125017070</v>
+        <v>125017076</v>
       </c>
       <c r="B32" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3795,10 +3819,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514333</v>
+        <v>514359</v>
       </c>
       <c r="R32" t="n">
-        <v>6741764</v>
+        <v>6742010</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3857,10 +3881,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125017034</v>
+        <v>125017071</v>
       </c>
       <c r="B33" t="n">
-        <v>8447</v>
+        <v>78947</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3869,43 +3893,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514346</v>
+        <v>514339</v>
       </c>
       <c r="R33" t="n">
-        <v>6741714</v>
+        <v>6741763</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3964,10 +3983,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125017082</v>
+        <v>125017055</v>
       </c>
       <c r="B34" t="n">
-        <v>92293</v>
+        <v>78947</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3976,47 +3995,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514343</v>
+        <v>514243</v>
       </c>
       <c r="R34" t="n">
-        <v>6741717</v>
+        <v>6741837</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4075,10 +4085,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125017015</v>
+        <v>125017045</v>
       </c>
       <c r="B35" t="n">
-        <v>96354</v>
+        <v>78947</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4091,21 +4101,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4115,10 +4125,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514225</v>
+        <v>514340</v>
       </c>
       <c r="R35" t="n">
-        <v>6741799</v>
+        <v>6741996</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4151,11 +4161,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4182,10 +4187,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125017084</v>
+        <v>125017031</v>
       </c>
       <c r="B36" t="n">
-        <v>96227</v>
+        <v>8447</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4198,34 +4203,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2869</v>
+        <v>106545</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514370</v>
+        <v>514358</v>
       </c>
       <c r="R36" t="n">
-        <v>6742063</v>
+        <v>6741952</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4284,10 +4294,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125017085</v>
+        <v>125017069</v>
       </c>
       <c r="B37" t="n">
-        <v>96227</v>
+        <v>78947</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4296,25 +4306,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4324,10 +4334,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514342</v>
+        <v>514232</v>
       </c>
       <c r="R37" t="n">
-        <v>6742146</v>
+        <v>6741754</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4386,10 +4396,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125017029</v>
+        <v>125017053</v>
       </c>
       <c r="B38" t="n">
-        <v>8447</v>
+        <v>78947</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4398,43 +4408,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514393</v>
+        <v>514273</v>
       </c>
       <c r="R38" t="n">
-        <v>6741939</v>
+        <v>6741841</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4493,10 +4498,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125017081</v>
+        <v>125017014</v>
       </c>
       <c r="B39" t="n">
-        <v>78810</v>
+        <v>75025</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4509,21 +4514,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4533,10 +4538,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514370</v>
+        <v>514311</v>
       </c>
       <c r="R39" t="n">
-        <v>6742029</v>
+        <v>6741920</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4595,10 +4600,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125017043</v>
+        <v>125017036</v>
       </c>
       <c r="B40" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4607,38 +4612,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514354</v>
+        <v>514293</v>
       </c>
       <c r="R40" t="n">
-        <v>6742044</v>
+        <v>6742097</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4697,10 +4711,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125017047</v>
+        <v>125017042</v>
       </c>
       <c r="B41" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4737,10 +4751,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514334</v>
+        <v>514331</v>
       </c>
       <c r="R41" t="n">
-        <v>6741981</v>
+        <v>6742061</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4799,10 +4813,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125017055</v>
+        <v>125017037</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>91184</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4815,21 +4829,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4839,10 +4853,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514243</v>
+        <v>514291</v>
       </c>
       <c r="R42" t="n">
-        <v>6741837</v>
+        <v>6741924</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4901,10 +4915,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125017071</v>
+        <v>125017052</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4941,10 +4955,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514339</v>
+        <v>514274</v>
       </c>
       <c r="R43" t="n">
-        <v>6741763</v>
+        <v>6741848</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5003,10 +5017,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125017088</v>
+        <v>125017027</v>
       </c>
       <c r="B44" t="n">
-        <v>5176</v>
+        <v>97147</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5019,21 +5033,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5043,10 +5057,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514339</v>
+        <v>514325</v>
       </c>
       <c r="R44" t="n">
-        <v>6741763</v>
+        <v>6742071</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5105,10 +5119,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125017036</v>
+        <v>125017013</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>79565</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5117,47 +5131,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514293</v>
+        <v>514345</v>
       </c>
       <c r="R45" t="n">
-        <v>6742097</v>
+        <v>6741942</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5216,10 +5221,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125017022</v>
+        <v>125017073</v>
       </c>
       <c r="B46" t="n">
-        <v>91012</v>
+        <v>78947</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5232,21 +5237,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5256,10 +5261,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514283</v>
+        <v>514387</v>
       </c>
       <c r="R46" t="n">
-        <v>6741836</v>
+        <v>6741982</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5318,10 +5323,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125017083</v>
+        <v>125017078</v>
       </c>
       <c r="B47" t="n">
-        <v>96227</v>
+        <v>78947</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5330,25 +5335,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5358,10 +5363,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514373</v>
+        <v>514359</v>
       </c>
       <c r="R47" t="n">
-        <v>6741951</v>
+        <v>6742012</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5420,10 +5425,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125017052</v>
+        <v>125017044</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5460,10 +5465,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514274</v>
+        <v>514351</v>
       </c>
       <c r="R48" t="n">
-        <v>6741848</v>
+        <v>6742013</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5522,7 +5527,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125017030</v>
+        <v>125017032</v>
       </c>
       <c r="B49" t="n">
         <v>8447</v>
@@ -5558,7 +5563,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5567,10 +5572,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514354</v>
+        <v>514330</v>
       </c>
       <c r="R49" t="n">
-        <v>6741952</v>
+        <v>6741874</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5629,10 +5634,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125017086</v>
+        <v>125017083</v>
       </c>
       <c r="B50" t="n">
-        <v>5176</v>
+        <v>96395</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5645,21 +5650,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100526</v>
+        <v>2869</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5669,10 +5674,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514306</v>
+        <v>514373</v>
       </c>
       <c r="R50" t="n">
-        <v>6741916</v>
+        <v>6741951</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5731,10 +5736,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125017033</v>
+        <v>125017074</v>
       </c>
       <c r="B51" t="n">
-        <v>8447</v>
+        <v>78947</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5743,43 +5748,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514336</v>
+        <v>514374</v>
       </c>
       <c r="R51" t="n">
-        <v>6741710</v>
+        <v>6741981</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5838,10 +5838,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125017069</v>
+        <v>125017086</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>5176</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5850,25 +5850,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5878,10 +5878,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514232</v>
+        <v>514306</v>
       </c>
       <c r="R52" t="n">
-        <v>6741754</v>
+        <v>6741916</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 15392-2025 artfynd.xlsx
+++ b/artfynd/A 15392-2025 artfynd.xlsx
@@ -2234,10 +2234,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017088</v>
+        <v>125017046</v>
       </c>
       <c r="B17" t="n">
-        <v>5176</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,25 +2246,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514339</v>
+        <v>514337</v>
       </c>
       <c r="R17" t="n">
-        <v>6741763</v>
+        <v>6741991</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,7 +2336,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017046</v>
+        <v>125017040</v>
       </c>
       <c r="B18" t="n">
         <v>78947</v>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514337</v>
+        <v>514327</v>
       </c>
       <c r="R18" t="n">
-        <v>6741991</v>
+        <v>6741885</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2412,6 +2412,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2438,10 +2443,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125017040</v>
+        <v>125017088</v>
       </c>
       <c r="B19" t="n">
-        <v>78947</v>
+        <v>5176</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,25 +2455,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2478,10 +2483,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514327</v>
+        <v>514339</v>
       </c>
       <c r="R19" t="n">
-        <v>6741885</v>
+        <v>6741763</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2514,11 +2519,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -4915,10 +4915,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125017052</v>
+        <v>125017027</v>
       </c>
       <c r="B43" t="n">
-        <v>78947</v>
+        <v>97147</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4927,25 +4927,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514274</v>
+        <v>514325</v>
       </c>
       <c r="R43" t="n">
-        <v>6741848</v>
+        <v>6742071</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5017,10 +5017,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125017027</v>
+        <v>125017013</v>
       </c>
       <c r="B44" t="n">
-        <v>97147</v>
+        <v>79565</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5029,25 +5029,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5057,10 +5057,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514325</v>
+        <v>514345</v>
       </c>
       <c r="R44" t="n">
-        <v>6742071</v>
+        <v>6741942</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5119,10 +5119,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125017013</v>
+        <v>125017052</v>
       </c>
       <c r="B45" t="n">
-        <v>79565</v>
+        <v>78947</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5135,21 +5135,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5159,10 +5159,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514345</v>
+        <v>514274</v>
       </c>
       <c r="R45" t="n">
-        <v>6741942</v>
+        <v>6741848</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 15392-2025 artfynd.xlsx
+++ b/artfynd/A 15392-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017051</v>
+        <v>125017015</v>
       </c>
       <c r="B2" t="n">
-        <v>78947</v>
+        <v>96522</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514337</v>
+        <v>514225</v>
       </c>
       <c r="R2" t="n">
-        <v>6741897</v>
+        <v>6741799</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017043</v>
+        <v>125017078</v>
       </c>
       <c r="B3" t="n">
         <v>78947</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514354</v>
+        <v>514359</v>
       </c>
       <c r="R3" t="n">
-        <v>6742044</v>
+        <v>6742012</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017041</v>
+        <v>125017083</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
+        <v>96395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514235</v>
+        <v>514373</v>
       </c>
       <c r="R4" t="n">
-        <v>6742182</v>
+        <v>6741951</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017082</v>
+        <v>125017055</v>
       </c>
       <c r="B5" t="n">
-        <v>92448</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,47 +998,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514343</v>
+        <v>514243</v>
       </c>
       <c r="R5" t="n">
-        <v>6741717</v>
+        <v>6741837</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017075</v>
+        <v>125017069</v>
       </c>
       <c r="B6" t="n">
         <v>78947</v>
@@ -1132,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514356</v>
+        <v>514232</v>
       </c>
       <c r="R6" t="n">
-        <v>6742004</v>
+        <v>6741754</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017035</v>
+        <v>125017022</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
+        <v>91166</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,43 +1202,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514366</v>
+        <v>514283</v>
       </c>
       <c r="R7" t="n">
-        <v>6741941</v>
+        <v>6741836</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017085</v>
+        <v>125017088</v>
       </c>
       <c r="B8" t="n">
-        <v>96395</v>
+        <v>5176</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2869</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514342</v>
+        <v>514339</v>
       </c>
       <c r="R8" t="n">
-        <v>6742146</v>
+        <v>6741763</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017025</v>
+        <v>125017021</v>
       </c>
       <c r="B9" t="n">
         <v>91166</v>
@@ -1443,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514390</v>
+        <v>514291</v>
       </c>
       <c r="R9" t="n">
-        <v>6741952</v>
+        <v>6741927</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017033</v>
+        <v>125017087</v>
       </c>
       <c r="B10" t="n">
-        <v>8447</v>
+        <v>5176</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,39 +1512,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514336</v>
+        <v>514358</v>
       </c>
       <c r="R10" t="n">
-        <v>6741710</v>
+        <v>6742011</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017029</v>
+        <v>125017076</v>
       </c>
       <c r="B11" t="n">
-        <v>8447</v>
+        <v>78947</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,43 +1610,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514393</v>
+        <v>514359</v>
       </c>
       <c r="R11" t="n">
-        <v>6741939</v>
+        <v>6742010</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017015</v>
+        <v>125017072</v>
       </c>
       <c r="B12" t="n">
-        <v>96522</v>
+        <v>78947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,21 +1716,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1759,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514225</v>
+        <v>514411</v>
       </c>
       <c r="R12" t="n">
-        <v>6741799</v>
+        <v>6741898</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,11 +1776,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1826,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017084</v>
+        <v>125017040</v>
       </c>
       <c r="B13" t="n">
-        <v>96395</v>
+        <v>78947</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1866,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514370</v>
+        <v>514327</v>
       </c>
       <c r="R13" t="n">
-        <v>6742063</v>
+        <v>6741885</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,6 +1878,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017048</v>
+        <v>125017014</v>
       </c>
       <c r="B14" t="n">
-        <v>78947</v>
+        <v>75025</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1944,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1968,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514295</v>
+        <v>514311</v>
       </c>
       <c r="R14" t="n">
-        <v>6741934</v>
+        <v>6741920</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,10 +2011,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017016</v>
+        <v>125017080</v>
       </c>
       <c r="B15" t="n">
-        <v>91131</v>
+        <v>78947</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,25 +2023,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2070,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514278</v>
+        <v>514363</v>
       </c>
       <c r="R15" t="n">
-        <v>6741831</v>
+        <v>6742014</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017050</v>
+        <v>125017029</v>
       </c>
       <c r="B16" t="n">
-        <v>78947</v>
+        <v>8447</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,38 +2125,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514318</v>
+        <v>514393</v>
       </c>
       <c r="R16" t="n">
-        <v>6741915</v>
+        <v>6741939</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2234,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017046</v>
+        <v>125017036</v>
       </c>
       <c r="B17" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,38 +2232,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514337</v>
+        <v>514293</v>
       </c>
       <c r="R17" t="n">
-        <v>6741991</v>
+        <v>6742097</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,7 +2331,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017040</v>
+        <v>125017051</v>
       </c>
       <c r="B18" t="n">
         <v>78947</v>
@@ -2376,10 +2371,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514327</v>
+        <v>514337</v>
       </c>
       <c r="R18" t="n">
-        <v>6741885</v>
+        <v>6741897</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2412,11 +2407,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2443,10 +2433,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125017088</v>
+        <v>125017048</v>
       </c>
       <c r="B19" t="n">
-        <v>5176</v>
+        <v>78947</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2455,25 +2445,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2483,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514339</v>
+        <v>514295</v>
       </c>
       <c r="R19" t="n">
-        <v>6741763</v>
+        <v>6741934</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,10 +2535,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125017021</v>
+        <v>125017047</v>
       </c>
       <c r="B20" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2561,21 +2551,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2585,10 +2575,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514291</v>
+        <v>514334</v>
       </c>
       <c r="R20" t="n">
-        <v>6741927</v>
+        <v>6741981</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2647,10 +2637,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125017080</v>
+        <v>125017030</v>
       </c>
       <c r="B21" t="n">
-        <v>78947</v>
+        <v>8447</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2659,38 +2649,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514363</v>
+        <v>514354</v>
       </c>
       <c r="R21" t="n">
-        <v>6742014</v>
+        <v>6741952</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2749,7 +2744,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125017081</v>
+        <v>125017046</v>
       </c>
       <c r="B22" t="n">
         <v>78947</v>
@@ -2789,10 +2784,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514370</v>
+        <v>514337</v>
       </c>
       <c r="R22" t="n">
-        <v>6742029</v>
+        <v>6741991</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2851,10 +2846,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125017047</v>
+        <v>125017037</v>
       </c>
       <c r="B23" t="n">
-        <v>78947</v>
+        <v>91184</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2867,21 +2862,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2891,10 +2886,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514334</v>
+        <v>514291</v>
       </c>
       <c r="R23" t="n">
-        <v>6741981</v>
+        <v>6741924</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2953,7 +2948,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125017054</v>
+        <v>125017050</v>
       </c>
       <c r="B24" t="n">
         <v>78947</v>
@@ -2993,10 +2988,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514257</v>
+        <v>514318</v>
       </c>
       <c r="R24" t="n">
-        <v>6741839</v>
+        <v>6741915</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3055,7 +3050,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125017087</v>
+        <v>125017086</v>
       </c>
       <c r="B25" t="n">
         <v>5176</v>
@@ -3095,10 +3090,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514358</v>
+        <v>514306</v>
       </c>
       <c r="R25" t="n">
-        <v>6742011</v>
+        <v>6741916</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3157,10 +3152,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125017034</v>
+        <v>125017025</v>
       </c>
       <c r="B26" t="n">
-        <v>8447</v>
+        <v>91166</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3169,43 +3164,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514346</v>
+        <v>514390</v>
       </c>
       <c r="R26" t="n">
-        <v>6741714</v>
+        <v>6741952</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3264,10 +3254,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125017030</v>
+        <v>125017074</v>
       </c>
       <c r="B27" t="n">
-        <v>8447</v>
+        <v>78947</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3276,43 +3266,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514354</v>
+        <v>514374</v>
       </c>
       <c r="R27" t="n">
-        <v>6741952</v>
+        <v>6741981</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3371,10 +3356,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125017022</v>
+        <v>125017084</v>
       </c>
       <c r="B28" t="n">
-        <v>91166</v>
+        <v>96395</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3383,25 +3368,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3411,10 +3396,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514283</v>
+        <v>514370</v>
       </c>
       <c r="R28" t="n">
-        <v>6741836</v>
+        <v>6742063</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3473,7 +3458,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125017072</v>
+        <v>125017054</v>
       </c>
       <c r="B29" t="n">
         <v>78947</v>
@@ -3513,10 +3498,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514411</v>
+        <v>514257</v>
       </c>
       <c r="R29" t="n">
-        <v>6741898</v>
+        <v>6741839</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3575,7 +3560,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125017070</v>
+        <v>125017045</v>
       </c>
       <c r="B30" t="n">
         <v>78947</v>
@@ -3615,10 +3600,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514333</v>
+        <v>514340</v>
       </c>
       <c r="R30" t="n">
-        <v>6741764</v>
+        <v>6741996</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3677,7 +3662,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125017049</v>
+        <v>125017075</v>
       </c>
       <c r="B31" t="n">
         <v>78947</v>
@@ -3717,10 +3702,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514311</v>
+        <v>514356</v>
       </c>
       <c r="R31" t="n">
-        <v>6741920</v>
+        <v>6742004</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3779,10 +3764,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125017076</v>
+        <v>125017035</v>
       </c>
       <c r="B32" t="n">
-        <v>78947</v>
+        <v>8447</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3791,38 +3776,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514359</v>
+        <v>514366</v>
       </c>
       <c r="R32" t="n">
-        <v>6742010</v>
+        <v>6741941</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3881,10 +3871,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125017071</v>
+        <v>125017032</v>
       </c>
       <c r="B33" t="n">
-        <v>78947</v>
+        <v>8447</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3893,38 +3883,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514339</v>
+        <v>514330</v>
       </c>
       <c r="R33" t="n">
-        <v>6741763</v>
+        <v>6741874</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3983,10 +3978,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125017055</v>
+        <v>125017031</v>
       </c>
       <c r="B34" t="n">
-        <v>78947</v>
+        <v>8447</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3995,38 +3990,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514243</v>
+        <v>514358</v>
       </c>
       <c r="R34" t="n">
-        <v>6741837</v>
+        <v>6741952</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125017045</v>
+        <v>125017073</v>
       </c>
       <c r="B35" t="n">
         <v>78947</v>
@@ -4125,10 +4125,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514340</v>
+        <v>514387</v>
       </c>
       <c r="R35" t="n">
-        <v>6741996</v>
+        <v>6741982</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4187,10 +4187,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125017031</v>
+        <v>125017013</v>
       </c>
       <c r="B36" t="n">
-        <v>8447</v>
+        <v>79565</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4199,43 +4199,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514358</v>
+        <v>514345</v>
       </c>
       <c r="R36" t="n">
-        <v>6741952</v>
+        <v>6741942</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4294,7 +4289,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125017069</v>
+        <v>125017042</v>
       </c>
       <c r="B37" t="n">
         <v>78947</v>
@@ -4334,10 +4329,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514232</v>
+        <v>514331</v>
       </c>
       <c r="R37" t="n">
-        <v>6741754</v>
+        <v>6742061</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4396,7 +4391,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125017053</v>
+        <v>125017070</v>
       </c>
       <c r="B38" t="n">
         <v>78947</v>
@@ -4436,10 +4431,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514273</v>
+        <v>514333</v>
       </c>
       <c r="R38" t="n">
-        <v>6741841</v>
+        <v>6741764</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4498,10 +4493,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125017014</v>
+        <v>125017085</v>
       </c>
       <c r="B39" t="n">
-        <v>75025</v>
+        <v>96395</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4510,25 +4505,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>2869</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4538,10 +4533,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514311</v>
+        <v>514342</v>
       </c>
       <c r="R39" t="n">
-        <v>6741920</v>
+        <v>6742146</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4600,10 +4595,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125017036</v>
+        <v>125017082</v>
       </c>
       <c r="B40" t="n">
-        <v>98269</v>
+        <v>92448</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4612,35 +4607,35 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4649,10 +4644,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514293</v>
+        <v>514343</v>
       </c>
       <c r="R40" t="n">
-        <v>6742097</v>
+        <v>6741717</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4711,7 +4706,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125017042</v>
+        <v>125017044</v>
       </c>
       <c r="B41" t="n">
         <v>78947</v>
@@ -4751,10 +4746,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514331</v>
+        <v>514351</v>
       </c>
       <c r="R41" t="n">
-        <v>6742061</v>
+        <v>6742013</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4813,10 +4808,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125017037</v>
+        <v>125017041</v>
       </c>
       <c r="B42" t="n">
-        <v>91184</v>
+        <v>78947</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4829,21 +4824,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4853,10 +4848,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514291</v>
+        <v>514235</v>
       </c>
       <c r="R42" t="n">
-        <v>6741924</v>
+        <v>6742182</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4915,10 +4910,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125017027</v>
+        <v>125017081</v>
       </c>
       <c r="B43" t="n">
-        <v>97147</v>
+        <v>78947</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4927,25 +4922,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4955,10 +4950,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514325</v>
+        <v>514370</v>
       </c>
       <c r="R43" t="n">
-        <v>6742071</v>
+        <v>6742029</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5017,10 +5012,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125017013</v>
+        <v>125017016</v>
       </c>
       <c r="B44" t="n">
-        <v>79565</v>
+        <v>91131</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5029,25 +5024,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5057,10 +5052,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514345</v>
+        <v>514278</v>
       </c>
       <c r="R44" t="n">
-        <v>6741942</v>
+        <v>6741831</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5119,10 +5114,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125017052</v>
+        <v>125017034</v>
       </c>
       <c r="B45" t="n">
-        <v>78947</v>
+        <v>8447</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5131,38 +5126,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514274</v>
+        <v>514346</v>
       </c>
       <c r="R45" t="n">
-        <v>6741848</v>
+        <v>6741714</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5221,7 +5221,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125017073</v>
+        <v>125017071</v>
       </c>
       <c r="B46" t="n">
         <v>78947</v>
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514387</v>
+        <v>514339</v>
       </c>
       <c r="R46" t="n">
-        <v>6741982</v>
+        <v>6741763</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5323,7 +5323,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125017078</v>
+        <v>125017043</v>
       </c>
       <c r="B47" t="n">
         <v>78947</v>
@@ -5363,10 +5363,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514359</v>
+        <v>514354</v>
       </c>
       <c r="R47" t="n">
-        <v>6742012</v>
+        <v>6742044</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5425,10 +5425,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125017044</v>
+        <v>125017027</v>
       </c>
       <c r="B48" t="n">
-        <v>78947</v>
+        <v>97147</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5437,25 +5437,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5465,10 +5465,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514351</v>
+        <v>514325</v>
       </c>
       <c r="R48" t="n">
-        <v>6742013</v>
+        <v>6742071</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5527,7 +5527,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125017032</v>
+        <v>125017033</v>
       </c>
       <c r="B49" t="n">
         <v>8447</v>
@@ -5572,10 +5572,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514330</v>
+        <v>514336</v>
       </c>
       <c r="R49" t="n">
-        <v>6741874</v>
+        <v>6741710</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5634,10 +5634,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125017083</v>
+        <v>125017052</v>
       </c>
       <c r="B50" t="n">
-        <v>96395</v>
+        <v>78947</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5646,25 +5646,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5674,10 +5674,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514373</v>
+        <v>514274</v>
       </c>
       <c r="R50" t="n">
-        <v>6741951</v>
+        <v>6741848</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5736,7 +5736,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125017074</v>
+        <v>125017053</v>
       </c>
       <c r="B51" t="n">
         <v>78947</v>
@@ -5776,10 +5776,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514374</v>
+        <v>514273</v>
       </c>
       <c r="R51" t="n">
-        <v>6741981</v>
+        <v>6741841</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5838,10 +5838,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125017086</v>
+        <v>125017049</v>
       </c>
       <c r="B52" t="n">
-        <v>5176</v>
+        <v>78947</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5850,25 +5850,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5878,10 +5878,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514306</v>
+        <v>514311</v>
       </c>
       <c r="R52" t="n">
-        <v>6741916</v>
+        <v>6741920</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>

--- a/artfynd/A 15392-2025 artfynd.xlsx
+++ b/artfynd/A 15392-2025 artfynd.xlsx
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017087</v>
+        <v>125017076</v>
       </c>
       <c r="B10" t="n">
-        <v>5176</v>
+        <v>78947</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514358</v>
+        <v>514359</v>
       </c>
       <c r="R10" t="n">
-        <v>6742011</v>
+        <v>6742010</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017076</v>
+        <v>125017072</v>
       </c>
       <c r="B11" t="n">
         <v>78947</v>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514359</v>
+        <v>514411</v>
       </c>
       <c r="R11" t="n">
-        <v>6742010</v>
+        <v>6741898</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,7 +1700,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017072</v>
+        <v>125017040</v>
       </c>
       <c r="B12" t="n">
         <v>78947</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514411</v>
+        <v>514327</v>
       </c>
       <c r="R12" t="n">
-        <v>6741898</v>
+        <v>6741885</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,6 +1776,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017040</v>
+        <v>125017087</v>
       </c>
       <c r="B13" t="n">
-        <v>78947</v>
+        <v>5176</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1819,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514327</v>
+        <v>514358</v>
       </c>
       <c r="R13" t="n">
-        <v>6741885</v>
+        <v>6742011</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,11 +1883,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2113,10 +2113,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017029</v>
+        <v>125017036</v>
       </c>
       <c r="B16" t="n">
-        <v>8447</v>
+        <v>98269</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2125,31 +2125,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2158,10 +2162,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514393</v>
+        <v>514293</v>
       </c>
       <c r="R16" t="n">
-        <v>6741939</v>
+        <v>6742097</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,10 +2224,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017036</v>
+        <v>125017029</v>
       </c>
       <c r="B17" t="n">
-        <v>98269</v>
+        <v>8447</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2232,35 +2236,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514293</v>
+        <v>514393</v>
       </c>
       <c r="R17" t="n">
-        <v>6742097</v>
+        <v>6741939</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -3662,10 +3662,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125017075</v>
+        <v>125017035</v>
       </c>
       <c r="B31" t="n">
-        <v>78947</v>
+        <v>8447</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3674,38 +3674,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514356</v>
+        <v>514366</v>
       </c>
       <c r="R31" t="n">
-        <v>6742004</v>
+        <v>6741941</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3764,7 +3769,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125017035</v>
+        <v>125017032</v>
       </c>
       <c r="B32" t="n">
         <v>8447</v>
@@ -3809,10 +3814,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514366</v>
+        <v>514330</v>
       </c>
       <c r="R32" t="n">
-        <v>6741941</v>
+        <v>6741874</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3871,10 +3876,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125017032</v>
+        <v>125017075</v>
       </c>
       <c r="B33" t="n">
-        <v>8447</v>
+        <v>78947</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3883,43 +3888,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514330</v>
+        <v>514356</v>
       </c>
       <c r="R33" t="n">
-        <v>6741874</v>
+        <v>6742004</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 15392-2025 artfynd.xlsx
+++ b/artfynd/A 15392-2025 artfynd.xlsx
@@ -3978,10 +3978,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125017031</v>
+        <v>125017073</v>
       </c>
       <c r="B34" t="n">
-        <v>8447</v>
+        <v>78947</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3990,43 +3990,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514358</v>
+        <v>514387</v>
       </c>
       <c r="R34" t="n">
-        <v>6741952</v>
+        <v>6741982</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4085,10 +4080,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125017073</v>
+        <v>125017031</v>
       </c>
       <c r="B35" t="n">
-        <v>78947</v>
+        <v>8447</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4097,38 +4092,43 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514387</v>
+        <v>514358</v>
       </c>
       <c r="R35" t="n">
-        <v>6741982</v>
+        <v>6741952</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 15392-2025 artfynd.xlsx
+++ b/artfynd/A 15392-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125017015</v>
+        <v>125017045</v>
       </c>
       <c r="B2" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514225</v>
+        <v>514340</v>
       </c>
       <c r="R2" t="n">
-        <v>6741799</v>
+        <v>6741996</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125017078</v>
+        <v>125017084</v>
       </c>
       <c r="B3" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514359</v>
+        <v>514370</v>
       </c>
       <c r="R3" t="n">
-        <v>6742012</v>
+        <v>6742063</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125017083</v>
+        <v>125017029</v>
       </c>
       <c r="B4" t="n">
-        <v>96395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,34 +880,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514373</v>
+        <v>514393</v>
       </c>
       <c r="R4" t="n">
-        <v>6741951</v>
+        <v>6741939</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,16 +971,11 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125017055</v>
+        <v>125017043</v>
       </c>
       <c r="B5" t="n">
         <v>78947</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1026,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514243</v>
+        <v>514354</v>
       </c>
       <c r="R5" t="n">
-        <v>6741837</v>
+        <v>6742044</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,16 +1068,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125017069</v>
+        <v>125017074</v>
       </c>
       <c r="B6" t="n">
         <v>78947</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1128,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514232</v>
+        <v>514374</v>
       </c>
       <c r="R6" t="n">
-        <v>6741754</v>
+        <v>6741981</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,15 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125017022</v>
+        <v>125017044</v>
       </c>
       <c r="B7" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514283</v>
+        <v>514351</v>
       </c>
       <c r="R7" t="n">
-        <v>6741836</v>
+        <v>6742013</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,37 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125017088</v>
+        <v>125017081</v>
       </c>
       <c r="B8" t="n">
-        <v>5176</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514339</v>
+        <v>514370</v>
       </c>
       <c r="R8" t="n">
-        <v>6741763</v>
+        <v>6742029</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,15 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125017021</v>
+        <v>125017047</v>
       </c>
       <c r="B9" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514291</v>
+        <v>514334</v>
       </c>
       <c r="R9" t="n">
-        <v>6741927</v>
+        <v>6741981</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,15 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125017076</v>
+        <v>125017021</v>
       </c>
       <c r="B10" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514359</v>
+        <v>514291</v>
       </c>
       <c r="R10" t="n">
-        <v>6742010</v>
+        <v>6741927</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,15 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125017072</v>
+        <v>125017013</v>
       </c>
       <c r="B11" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1614,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514411</v>
+        <v>514345</v>
       </c>
       <c r="R11" t="n">
-        <v>6741898</v>
+        <v>6741942</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,16 +1650,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125017040</v>
+        <v>125017070</v>
       </c>
       <c r="B12" t="n">
         <v>78947</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1740,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514327</v>
+        <v>514333</v>
       </c>
       <c r="R12" t="n">
-        <v>6741885</v>
+        <v>6741764</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,11 +1721,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-11</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1807,37 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125017087</v>
+        <v>125017075</v>
       </c>
       <c r="B13" t="n">
-        <v>5176</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1847,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514358</v>
+        <v>514356</v>
       </c>
       <c r="R13" t="n">
-        <v>6742011</v>
+        <v>6742004</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1909,15 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125017014</v>
+        <v>125017042</v>
       </c>
       <c r="B14" t="n">
-        <v>75025</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1925,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514311</v>
+        <v>514331</v>
       </c>
       <c r="R14" t="n">
-        <v>6741920</v>
+        <v>6742061</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,16 +1941,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125017080</v>
+        <v>125017051</v>
       </c>
       <c r="B15" t="n">
         <v>78947</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2051,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514363</v>
+        <v>514337</v>
       </c>
       <c r="R15" t="n">
-        <v>6742014</v>
+        <v>6741897</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,59 +2038,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125017036</v>
+        <v>125017048</v>
       </c>
       <c r="B16" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514293</v>
+        <v>514295</v>
       </c>
       <c r="R16" t="n">
-        <v>6742097</v>
+        <v>6741934</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2224,55 +2135,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125017029</v>
+        <v>125017078</v>
       </c>
       <c r="B17" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514393</v>
+        <v>514359</v>
       </c>
       <c r="R17" t="n">
-        <v>6741939</v>
+        <v>6742012</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2331,37 +2232,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125017051</v>
+        <v>125017083</v>
       </c>
       <c r="B18" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96395</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2371,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514337</v>
+        <v>514373</v>
       </c>
       <c r="R18" t="n">
-        <v>6741897</v>
+        <v>6741951</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2433,16 +2329,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125017048</v>
+        <v>125017049</v>
       </c>
       <c r="B19" t="n">
         <v>78947</v>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2473,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514295</v>
+        <v>514311</v>
       </c>
       <c r="R19" t="n">
-        <v>6741934</v>
+        <v>6741920</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,50 +2426,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125017047</v>
+        <v>125017031</v>
       </c>
       <c r="B20" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8447</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514334</v>
+        <v>514358</v>
       </c>
       <c r="R20" t="n">
-        <v>6741981</v>
+        <v>6741952</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,15 +2528,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125017030</v>
+        <v>125017085</v>
       </c>
       <c r="B21" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96395</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2653,39 +2539,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>2869</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514354</v>
+        <v>514342</v>
       </c>
       <c r="R21" t="n">
-        <v>6741952</v>
+        <v>6742146</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2744,15 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125017046</v>
+        <v>125017025</v>
       </c>
       <c r="B22" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2760,21 +2636,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2784,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514337</v>
+        <v>514390</v>
       </c>
       <c r="R22" t="n">
-        <v>6741991</v>
+        <v>6741952</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,15 +2722,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125017037</v>
+        <v>125017071</v>
       </c>
       <c r="B23" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2862,21 +2733,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2886,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514291</v>
+        <v>514339</v>
       </c>
       <c r="R23" t="n">
-        <v>6741924</v>
+        <v>6741763</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,16 +2819,11 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125017050</v>
+        <v>125017041</v>
       </c>
       <c r="B24" t="n">
         <v>78947</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>NT</t>
@@ -2988,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514318</v>
+        <v>514235</v>
       </c>
       <c r="R24" t="n">
-        <v>6741915</v>
+        <v>6742182</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3050,37 +2916,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125017086</v>
+        <v>125017069</v>
       </c>
       <c r="B25" t="n">
-        <v>5176</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3090,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514306</v>
+        <v>514232</v>
       </c>
       <c r="R25" t="n">
-        <v>6741916</v>
+        <v>6741754</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,15 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125017025</v>
+        <v>125017072</v>
       </c>
       <c r="B26" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3168,21 +3024,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3192,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514390</v>
+        <v>514411</v>
       </c>
       <c r="R26" t="n">
-        <v>6741952</v>
+        <v>6741898</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3254,50 +3110,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125017074</v>
+        <v>125017082</v>
       </c>
       <c r="B27" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92448</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514374</v>
+        <v>514343</v>
       </c>
       <c r="R27" t="n">
-        <v>6741981</v>
+        <v>6741717</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3356,37 +3216,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125017084</v>
+        <v>125017055</v>
       </c>
       <c r="B28" t="n">
-        <v>96395</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3396,10 +3251,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514370</v>
+        <v>514243</v>
       </c>
       <c r="R28" t="n">
-        <v>6742063</v>
+        <v>6741837</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3458,16 +3313,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125017054</v>
+        <v>125017053</v>
       </c>
       <c r="B29" t="n">
         <v>78947</v>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>NT</t>
@@ -3498,10 +3348,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>514257</v>
+        <v>514273</v>
       </c>
       <c r="R29" t="n">
-        <v>6741839</v>
+        <v>6741841</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3560,15 +3410,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125017045</v>
+        <v>125017037</v>
       </c>
       <c r="B30" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91184</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3576,21 +3421,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3600,10 +3445,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>514340</v>
+        <v>514291</v>
       </c>
       <c r="R30" t="n">
-        <v>6741996</v>
+        <v>6741924</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3662,55 +3507,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125017035</v>
+        <v>125017015</v>
       </c>
       <c r="B31" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96522</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>514366</v>
+        <v>514225</v>
       </c>
       <c r="R31" t="n">
-        <v>6741941</v>
+        <v>6741799</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3743,6 +3578,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På låga i röjd sumpskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3769,16 +3609,11 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125017032</v>
+        <v>125017033</v>
       </c>
       <c r="B32" t="n">
         <v>8447</v>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D32" t="inlineStr">
         <is>
           <t>LC</t>
@@ -3814,10 +3649,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>514330</v>
+        <v>514336</v>
       </c>
       <c r="R32" t="n">
-        <v>6741874</v>
+        <v>6741710</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3876,50 +3711,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125017075</v>
+        <v>125017035</v>
       </c>
       <c r="B33" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8447</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>514356</v>
+        <v>514366</v>
       </c>
       <c r="R33" t="n">
-        <v>6742004</v>
+        <v>6741941</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3978,37 +3813,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125017073</v>
+        <v>125017087</v>
       </c>
       <c r="B34" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5176</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4018,10 +3848,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>514387</v>
+        <v>514358</v>
       </c>
       <c r="R34" t="n">
-        <v>6741982</v>
+        <v>6742011</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4080,15 +3910,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125017031</v>
+        <v>125017086</v>
       </c>
       <c r="B35" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5176</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4096,39 +3921,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>514358</v>
+        <v>514306</v>
       </c>
       <c r="R35" t="n">
-        <v>6741952</v>
+        <v>6741916</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4187,15 +4007,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125017013</v>
+        <v>125017080</v>
       </c>
       <c r="B36" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4203,21 +4018,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4227,10 +4042,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>514345</v>
+        <v>514363</v>
       </c>
       <c r="R36" t="n">
-        <v>6741942</v>
+        <v>6742014</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4289,50 +4104,50 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125017042</v>
+        <v>125017030</v>
       </c>
       <c r="B37" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514331</v>
+        <v>514354</v>
       </c>
       <c r="R37" t="n">
-        <v>6742061</v>
+        <v>6741952</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4391,15 +4206,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125017070</v>
+        <v>125017014</v>
       </c>
       <c r="B38" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75025</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4407,21 +4217,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4431,10 +4241,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514333</v>
+        <v>514311</v>
       </c>
       <c r="R38" t="n">
-        <v>6741764</v>
+        <v>6741920</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4493,37 +4303,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125017085</v>
+        <v>125017076</v>
       </c>
       <c r="B39" t="n">
-        <v>96395</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4533,10 +4338,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514342</v>
+        <v>514359</v>
       </c>
       <c r="R39" t="n">
-        <v>6742146</v>
+        <v>6742010</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4595,59 +4400,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125017082</v>
+        <v>125017046</v>
       </c>
       <c r="B40" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514343</v>
+        <v>514337</v>
       </c>
       <c r="R40" t="n">
-        <v>6741717</v>
+        <v>6741991</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4706,50 +4497,54 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125017044</v>
+        <v>125017036</v>
       </c>
       <c r="B41" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514351</v>
+        <v>514293</v>
       </c>
       <c r="R41" t="n">
-        <v>6742013</v>
+        <v>6742097</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4808,15 +4603,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125017041</v>
+        <v>125017022</v>
       </c>
       <c r="B42" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91166</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4824,21 +4614,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4848,10 +4638,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514235</v>
+        <v>514283</v>
       </c>
       <c r="R42" t="n">
-        <v>6742182</v>
+        <v>6741836</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4910,37 +4700,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125017081</v>
+        <v>125017016</v>
       </c>
       <c r="B43" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91131</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4950,10 +4735,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514370</v>
+        <v>514278</v>
       </c>
       <c r="R43" t="n">
-        <v>6742029</v>
+        <v>6741831</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5012,15 +4797,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125017016</v>
+        <v>125017032</v>
       </c>
       <c r="B44" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8447</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5028,34 +4808,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514278</v>
+        <v>514330</v>
       </c>
       <c r="R44" t="n">
-        <v>6741831</v>
+        <v>6741874</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5114,55 +4899,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125017034</v>
+        <v>125017054</v>
       </c>
       <c r="B45" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514346</v>
+        <v>514257</v>
       </c>
       <c r="R45" t="n">
-        <v>6741714</v>
+        <v>6741839</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5221,16 +4996,11 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125017071</v>
+        <v>125017052</v>
       </c>
       <c r="B46" t="n">
         <v>78947</v>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D46" t="inlineStr">
         <is>
           <t>NT</t>
@@ -5261,10 +5031,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514339</v>
+        <v>514274</v>
       </c>
       <c r="R46" t="n">
-        <v>6741763</v>
+        <v>6741848</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5323,16 +5093,11 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125017043</v>
+        <v>125017073</v>
       </c>
       <c r="B47" t="n">
         <v>78947</v>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D47" t="inlineStr">
         <is>
           <t>NT</t>
@@ -5363,10 +5128,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514354</v>
+        <v>514387</v>
       </c>
       <c r="R47" t="n">
-        <v>6742044</v>
+        <v>6741982</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5425,15 +5190,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125017027</v>
+        <v>125017088</v>
       </c>
       <c r="B48" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5176</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5441,21 +5201,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5465,10 +5225,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514325</v>
+        <v>514339</v>
       </c>
       <c r="R48" t="n">
-        <v>6742071</v>
+        <v>6741763</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5527,55 +5287,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125017033</v>
+        <v>125017040</v>
       </c>
       <c r="B49" t="n">
-        <v>8447</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514336</v>
+        <v>514327</v>
       </c>
       <c r="R49" t="n">
-        <v>6741710</v>
+        <v>6741885</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5608,6 +5358,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Rikligt på röjd undertryckt gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5634,50 +5389,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125017052</v>
+        <v>125017034</v>
       </c>
       <c r="B50" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8447</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Tamptjärnsån, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514274</v>
+        <v>514346</v>
       </c>
       <c r="R50" t="n">
-        <v>6741848</v>
+        <v>6741714</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5736,37 +5491,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125017053</v>
+        <v>125017027</v>
       </c>
       <c r="B51" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97147</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5776,10 +5526,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514273</v>
+        <v>514325</v>
       </c>
       <c r="R51" t="n">
-        <v>6741841</v>
+        <v>6742071</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5838,16 +5588,11 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125017049</v>
+        <v>125017050</v>
       </c>
       <c r="B52" t="n">
         <v>78947</v>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>NT</t>
@@ -5878,10 +5623,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514311</v>
+        <v>514318</v>
       </c>
       <c r="R52" t="n">
-        <v>6741920</v>
+        <v>6741915</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
